--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF820247-B4B1-49F9-A49C-CCF3F22217DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C257B2D-B9B8-43A1-9BE8-E056BB618DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4208,7 +4208,7 @@
         <v>4</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>26</v>
@@ -4237,7 +4237,7 @@
         <v>5</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>26</v>
@@ -4324,7 +4324,7 @@
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>26</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C257B2D-B9B8-43A1-9BE8-E056BB618DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F424D6A-2D65-480F-A7EA-2D33E282B863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_rand_rule_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="34">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,6 +152,13 @@
   </si>
   <si>
     <t>1:100_2:100_3:100_4:100_5:100_11:10000_12:100000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201:100_202:100_203:100_204:100_205:100</t>
+  </si>
+  <si>
+    <t>201:100_202:100_203:100_204:100_205:100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -528,7 +535,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I204"/>
+  <dimension ref="A1:I264"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" style="5" bestFit="1" customWidth="1"/>
@@ -6430,6 +6437,1746 @@
         <v>28</v>
       </c>
     </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A205" s="5">
+        <v>1010001</v>
+      </c>
+      <c r="B205" s="5">
+        <v>101</v>
+      </c>
+      <c r="C205" s="5">
+        <v>1</v>
+      </c>
+      <c r="D205" t="s">
+        <v>33</v>
+      </c>
+      <c r="E205" t="s">
+        <v>32</v>
+      </c>
+      <c r="F205" t="s">
+        <v>32</v>
+      </c>
+      <c r="G205" t="s">
+        <v>32</v>
+      </c>
+      <c r="H205" t="s">
+        <v>32</v>
+      </c>
+      <c r="I205" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A206" s="5">
+        <v>1010002</v>
+      </c>
+      <c r="B206" s="5">
+        <v>101</v>
+      </c>
+      <c r="C206" s="5">
+        <v>2</v>
+      </c>
+      <c r="D206" t="s">
+        <v>32</v>
+      </c>
+      <c r="E206" t="s">
+        <v>32</v>
+      </c>
+      <c r="F206" t="s">
+        <v>32</v>
+      </c>
+      <c r="G206" t="s">
+        <v>32</v>
+      </c>
+      <c r="H206" t="s">
+        <v>32</v>
+      </c>
+      <c r="I206" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A207" s="5">
+        <v>1010003</v>
+      </c>
+      <c r="B207" s="5">
+        <v>101</v>
+      </c>
+      <c r="C207" s="5">
+        <v>3</v>
+      </c>
+      <c r="D207" t="s">
+        <v>32</v>
+      </c>
+      <c r="E207" t="s">
+        <v>32</v>
+      </c>
+      <c r="F207" t="s">
+        <v>32</v>
+      </c>
+      <c r="G207" t="s">
+        <v>32</v>
+      </c>
+      <c r="H207" t="s">
+        <v>32</v>
+      </c>
+      <c r="I207" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A208" s="5">
+        <v>1010004</v>
+      </c>
+      <c r="B208" s="5">
+        <v>101</v>
+      </c>
+      <c r="C208" s="5">
+        <v>4</v>
+      </c>
+      <c r="D208" t="s">
+        <v>32</v>
+      </c>
+      <c r="E208" t="s">
+        <v>32</v>
+      </c>
+      <c r="F208" t="s">
+        <v>32</v>
+      </c>
+      <c r="G208" t="s">
+        <v>32</v>
+      </c>
+      <c r="H208" t="s">
+        <v>32</v>
+      </c>
+      <c r="I208" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A209" s="5">
+        <v>1010005</v>
+      </c>
+      <c r="B209" s="5">
+        <v>101</v>
+      </c>
+      <c r="C209" s="5">
+        <v>5</v>
+      </c>
+      <c r="D209" t="s">
+        <v>32</v>
+      </c>
+      <c r="E209" t="s">
+        <v>32</v>
+      </c>
+      <c r="F209" t="s">
+        <v>32</v>
+      </c>
+      <c r="G209" t="s">
+        <v>32</v>
+      </c>
+      <c r="H209" t="s">
+        <v>32</v>
+      </c>
+      <c r="I209" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A210" s="5">
+        <v>1010006</v>
+      </c>
+      <c r="B210" s="5">
+        <v>101</v>
+      </c>
+      <c r="C210" s="5">
+        <v>6</v>
+      </c>
+      <c r="D210" t="s">
+        <v>32</v>
+      </c>
+      <c r="E210" t="s">
+        <v>32</v>
+      </c>
+      <c r="F210" t="s">
+        <v>32</v>
+      </c>
+      <c r="G210" t="s">
+        <v>32</v>
+      </c>
+      <c r="H210" t="s">
+        <v>32</v>
+      </c>
+      <c r="I210" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A211" s="5">
+        <v>1010007</v>
+      </c>
+      <c r="B211" s="5">
+        <v>101</v>
+      </c>
+      <c r="C211" s="5">
+        <v>7</v>
+      </c>
+      <c r="D211" t="s">
+        <v>32</v>
+      </c>
+      <c r="E211" t="s">
+        <v>32</v>
+      </c>
+      <c r="F211" t="s">
+        <v>32</v>
+      </c>
+      <c r="G211" t="s">
+        <v>32</v>
+      </c>
+      <c r="H211" t="s">
+        <v>32</v>
+      </c>
+      <c r="I211" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A212" s="5">
+        <v>1010008</v>
+      </c>
+      <c r="B212" s="5">
+        <v>101</v>
+      </c>
+      <c r="C212" s="5">
+        <v>8</v>
+      </c>
+      <c r="D212" t="s">
+        <v>32</v>
+      </c>
+      <c r="E212" t="s">
+        <v>32</v>
+      </c>
+      <c r="F212" t="s">
+        <v>32</v>
+      </c>
+      <c r="G212" t="s">
+        <v>32</v>
+      </c>
+      <c r="H212" t="s">
+        <v>32</v>
+      </c>
+      <c r="I212" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A213" s="5">
+        <v>1010009</v>
+      </c>
+      <c r="B213" s="5">
+        <v>101</v>
+      </c>
+      <c r="C213" s="5">
+        <v>9</v>
+      </c>
+      <c r="D213" t="s">
+        <v>32</v>
+      </c>
+      <c r="E213" t="s">
+        <v>32</v>
+      </c>
+      <c r="F213" t="s">
+        <v>32</v>
+      </c>
+      <c r="G213" t="s">
+        <v>32</v>
+      </c>
+      <c r="H213" t="s">
+        <v>32</v>
+      </c>
+      <c r="I213" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A214" s="5">
+        <v>1010010</v>
+      </c>
+      <c r="B214" s="5">
+        <v>101</v>
+      </c>
+      <c r="C214" s="5">
+        <v>10</v>
+      </c>
+      <c r="D214" t="s">
+        <v>32</v>
+      </c>
+      <c r="E214" t="s">
+        <v>32</v>
+      </c>
+      <c r="F214" t="s">
+        <v>32</v>
+      </c>
+      <c r="G214" t="s">
+        <v>32</v>
+      </c>
+      <c r="H214" t="s">
+        <v>32</v>
+      </c>
+      <c r="I214" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A215" s="5">
+        <v>1010011</v>
+      </c>
+      <c r="B215" s="5">
+        <v>101</v>
+      </c>
+      <c r="C215" s="5">
+        <v>11</v>
+      </c>
+      <c r="D215" t="s">
+        <v>32</v>
+      </c>
+      <c r="E215" t="s">
+        <v>32</v>
+      </c>
+      <c r="F215" t="s">
+        <v>32</v>
+      </c>
+      <c r="G215" t="s">
+        <v>32</v>
+      </c>
+      <c r="H215" t="s">
+        <v>32</v>
+      </c>
+      <c r="I215" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A216" s="5">
+        <v>1010012</v>
+      </c>
+      <c r="B216" s="5">
+        <v>101</v>
+      </c>
+      <c r="C216" s="5">
+        <v>12</v>
+      </c>
+      <c r="D216" t="s">
+        <v>32</v>
+      </c>
+      <c r="E216" t="s">
+        <v>32</v>
+      </c>
+      <c r="F216" t="s">
+        <v>32</v>
+      </c>
+      <c r="G216" t="s">
+        <v>32</v>
+      </c>
+      <c r="H216" t="s">
+        <v>32</v>
+      </c>
+      <c r="I216" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A217" s="5">
+        <v>1010013</v>
+      </c>
+      <c r="B217" s="5">
+        <v>101</v>
+      </c>
+      <c r="C217" s="5">
+        <v>13</v>
+      </c>
+      <c r="D217" t="s">
+        <v>32</v>
+      </c>
+      <c r="E217" t="s">
+        <v>32</v>
+      </c>
+      <c r="F217" t="s">
+        <v>32</v>
+      </c>
+      <c r="G217" t="s">
+        <v>32</v>
+      </c>
+      <c r="H217" t="s">
+        <v>32</v>
+      </c>
+      <c r="I217" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A218" s="5">
+        <v>1010014</v>
+      </c>
+      <c r="B218" s="5">
+        <v>101</v>
+      </c>
+      <c r="C218" s="5">
+        <v>14</v>
+      </c>
+      <c r="D218" t="s">
+        <v>32</v>
+      </c>
+      <c r="E218" t="s">
+        <v>32</v>
+      </c>
+      <c r="F218" t="s">
+        <v>32</v>
+      </c>
+      <c r="G218" t="s">
+        <v>32</v>
+      </c>
+      <c r="H218" t="s">
+        <v>32</v>
+      </c>
+      <c r="I218" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A219" s="5">
+        <v>1010015</v>
+      </c>
+      <c r="B219" s="5">
+        <v>101</v>
+      </c>
+      <c r="C219" s="5">
+        <v>15</v>
+      </c>
+      <c r="D219" t="s">
+        <v>32</v>
+      </c>
+      <c r="E219" t="s">
+        <v>32</v>
+      </c>
+      <c r="F219" t="s">
+        <v>32</v>
+      </c>
+      <c r="G219" t="s">
+        <v>32</v>
+      </c>
+      <c r="H219" t="s">
+        <v>32</v>
+      </c>
+      <c r="I219" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A220" s="5">
+        <v>1010016</v>
+      </c>
+      <c r="B220" s="5">
+        <v>101</v>
+      </c>
+      <c r="C220" s="5">
+        <v>16</v>
+      </c>
+      <c r="D220" t="s">
+        <v>32</v>
+      </c>
+      <c r="E220" t="s">
+        <v>32</v>
+      </c>
+      <c r="F220" t="s">
+        <v>32</v>
+      </c>
+      <c r="G220" t="s">
+        <v>32</v>
+      </c>
+      <c r="H220" t="s">
+        <v>32</v>
+      </c>
+      <c r="I220" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A221" s="5">
+        <v>1010017</v>
+      </c>
+      <c r="B221" s="5">
+        <v>101</v>
+      </c>
+      <c r="C221" s="5">
+        <v>17</v>
+      </c>
+      <c r="D221" t="s">
+        <v>32</v>
+      </c>
+      <c r="E221" t="s">
+        <v>32</v>
+      </c>
+      <c r="F221" t="s">
+        <v>32</v>
+      </c>
+      <c r="G221" t="s">
+        <v>32</v>
+      </c>
+      <c r="H221" t="s">
+        <v>32</v>
+      </c>
+      <c r="I221" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A222" s="5">
+        <v>1010018</v>
+      </c>
+      <c r="B222" s="5">
+        <v>101</v>
+      </c>
+      <c r="C222" s="5">
+        <v>18</v>
+      </c>
+      <c r="D222" t="s">
+        <v>32</v>
+      </c>
+      <c r="E222" t="s">
+        <v>32</v>
+      </c>
+      <c r="F222" t="s">
+        <v>32</v>
+      </c>
+      <c r="G222" t="s">
+        <v>32</v>
+      </c>
+      <c r="H222" t="s">
+        <v>32</v>
+      </c>
+      <c r="I222" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A223" s="5">
+        <v>1010019</v>
+      </c>
+      <c r="B223" s="5">
+        <v>101</v>
+      </c>
+      <c r="C223" s="5">
+        <v>19</v>
+      </c>
+      <c r="D223" t="s">
+        <v>32</v>
+      </c>
+      <c r="E223" t="s">
+        <v>32</v>
+      </c>
+      <c r="F223" t="s">
+        <v>32</v>
+      </c>
+      <c r="G223" t="s">
+        <v>32</v>
+      </c>
+      <c r="H223" t="s">
+        <v>32</v>
+      </c>
+      <c r="I223" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A224" s="5">
+        <v>1010020</v>
+      </c>
+      <c r="B224" s="5">
+        <v>101</v>
+      </c>
+      <c r="C224" s="5">
+        <v>20</v>
+      </c>
+      <c r="D224" t="s">
+        <v>32</v>
+      </c>
+      <c r="E224" t="s">
+        <v>32</v>
+      </c>
+      <c r="F224" t="s">
+        <v>32</v>
+      </c>
+      <c r="G224" t="s">
+        <v>32</v>
+      </c>
+      <c r="H224" t="s">
+        <v>32</v>
+      </c>
+      <c r="I224" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A225" s="5">
+        <v>1010021</v>
+      </c>
+      <c r="B225" s="5">
+        <v>101</v>
+      </c>
+      <c r="C225" s="5">
+        <v>21</v>
+      </c>
+      <c r="D225" t="s">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>32</v>
+      </c>
+      <c r="G225" t="s">
+        <v>32</v>
+      </c>
+      <c r="H225" t="s">
+        <v>32</v>
+      </c>
+      <c r="I225" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A226" s="5">
+        <v>1010022</v>
+      </c>
+      <c r="B226" s="5">
+        <v>101</v>
+      </c>
+      <c r="C226" s="5">
+        <v>22</v>
+      </c>
+      <c r="D226" t="s">
+        <v>32</v>
+      </c>
+      <c r="E226" t="s">
+        <v>32</v>
+      </c>
+      <c r="F226" t="s">
+        <v>32</v>
+      </c>
+      <c r="G226" t="s">
+        <v>32</v>
+      </c>
+      <c r="H226" t="s">
+        <v>32</v>
+      </c>
+      <c r="I226" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A227" s="5">
+        <v>1010023</v>
+      </c>
+      <c r="B227" s="5">
+        <v>101</v>
+      </c>
+      <c r="C227" s="5">
+        <v>23</v>
+      </c>
+      <c r="D227" t="s">
+        <v>32</v>
+      </c>
+      <c r="E227" t="s">
+        <v>32</v>
+      </c>
+      <c r="F227" t="s">
+        <v>32</v>
+      </c>
+      <c r="G227" t="s">
+        <v>32</v>
+      </c>
+      <c r="H227" t="s">
+        <v>32</v>
+      </c>
+      <c r="I227" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A228" s="5">
+        <v>1010024</v>
+      </c>
+      <c r="B228" s="5">
+        <v>101</v>
+      </c>
+      <c r="C228" s="5">
+        <v>24</v>
+      </c>
+      <c r="D228" t="s">
+        <v>32</v>
+      </c>
+      <c r="E228" t="s">
+        <v>32</v>
+      </c>
+      <c r="F228" t="s">
+        <v>32</v>
+      </c>
+      <c r="G228" t="s">
+        <v>32</v>
+      </c>
+      <c r="H228" t="s">
+        <v>32</v>
+      </c>
+      <c r="I228" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A229" s="5">
+        <v>1010025</v>
+      </c>
+      <c r="B229" s="5">
+        <v>101</v>
+      </c>
+      <c r="C229" s="5">
+        <v>25</v>
+      </c>
+      <c r="D229" t="s">
+        <v>32</v>
+      </c>
+      <c r="E229" t="s">
+        <v>32</v>
+      </c>
+      <c r="F229" t="s">
+        <v>32</v>
+      </c>
+      <c r="G229" t="s">
+        <v>32</v>
+      </c>
+      <c r="H229" t="s">
+        <v>32</v>
+      </c>
+      <c r="I229" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A230" s="5">
+        <v>1010026</v>
+      </c>
+      <c r="B230" s="5">
+        <v>101</v>
+      </c>
+      <c r="C230" s="5">
+        <v>26</v>
+      </c>
+      <c r="D230" t="s">
+        <v>32</v>
+      </c>
+      <c r="E230" t="s">
+        <v>32</v>
+      </c>
+      <c r="F230" t="s">
+        <v>32</v>
+      </c>
+      <c r="G230" t="s">
+        <v>32</v>
+      </c>
+      <c r="H230" t="s">
+        <v>32</v>
+      </c>
+      <c r="I230" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A231" s="5">
+        <v>1010027</v>
+      </c>
+      <c r="B231" s="5">
+        <v>101</v>
+      </c>
+      <c r="C231" s="5">
+        <v>27</v>
+      </c>
+      <c r="D231" t="s">
+        <v>32</v>
+      </c>
+      <c r="E231" t="s">
+        <v>32</v>
+      </c>
+      <c r="F231" t="s">
+        <v>32</v>
+      </c>
+      <c r="G231" t="s">
+        <v>32</v>
+      </c>
+      <c r="H231" t="s">
+        <v>32</v>
+      </c>
+      <c r="I231" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A232" s="5">
+        <v>1010028</v>
+      </c>
+      <c r="B232" s="5">
+        <v>101</v>
+      </c>
+      <c r="C232" s="5">
+        <v>28</v>
+      </c>
+      <c r="D232" t="s">
+        <v>32</v>
+      </c>
+      <c r="E232" t="s">
+        <v>32</v>
+      </c>
+      <c r="F232" t="s">
+        <v>32</v>
+      </c>
+      <c r="G232" t="s">
+        <v>32</v>
+      </c>
+      <c r="H232" t="s">
+        <v>32</v>
+      </c>
+      <c r="I232" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A233" s="5">
+        <v>1010029</v>
+      </c>
+      <c r="B233" s="5">
+        <v>101</v>
+      </c>
+      <c r="C233" s="5">
+        <v>29</v>
+      </c>
+      <c r="D233" t="s">
+        <v>32</v>
+      </c>
+      <c r="E233" t="s">
+        <v>32</v>
+      </c>
+      <c r="F233" t="s">
+        <v>32</v>
+      </c>
+      <c r="G233" t="s">
+        <v>32</v>
+      </c>
+      <c r="H233" t="s">
+        <v>32</v>
+      </c>
+      <c r="I233" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A234" s="5">
+        <v>1010030</v>
+      </c>
+      <c r="B234" s="5">
+        <v>101</v>
+      </c>
+      <c r="C234" s="5">
+        <v>30</v>
+      </c>
+      <c r="D234" t="s">
+        <v>32</v>
+      </c>
+      <c r="E234" t="s">
+        <v>32</v>
+      </c>
+      <c r="F234" t="s">
+        <v>32</v>
+      </c>
+      <c r="G234" t="s">
+        <v>32</v>
+      </c>
+      <c r="H234" t="s">
+        <v>32</v>
+      </c>
+      <c r="I234" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A235" s="5">
+        <v>1010031</v>
+      </c>
+      <c r="B235" s="5">
+        <v>101</v>
+      </c>
+      <c r="C235" s="5">
+        <v>31</v>
+      </c>
+      <c r="D235" t="s">
+        <v>32</v>
+      </c>
+      <c r="E235" t="s">
+        <v>32</v>
+      </c>
+      <c r="F235" t="s">
+        <v>32</v>
+      </c>
+      <c r="G235" t="s">
+        <v>32</v>
+      </c>
+      <c r="H235" t="s">
+        <v>32</v>
+      </c>
+      <c r="I235" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A236" s="5">
+        <v>1010032</v>
+      </c>
+      <c r="B236" s="5">
+        <v>101</v>
+      </c>
+      <c r="C236" s="5">
+        <v>32</v>
+      </c>
+      <c r="D236" t="s">
+        <v>32</v>
+      </c>
+      <c r="E236" t="s">
+        <v>32</v>
+      </c>
+      <c r="F236" t="s">
+        <v>32</v>
+      </c>
+      <c r="G236" t="s">
+        <v>32</v>
+      </c>
+      <c r="H236" t="s">
+        <v>32</v>
+      </c>
+      <c r="I236" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A237" s="5">
+        <v>1010033</v>
+      </c>
+      <c r="B237" s="5">
+        <v>101</v>
+      </c>
+      <c r="C237" s="5">
+        <v>33</v>
+      </c>
+      <c r="D237" t="s">
+        <v>32</v>
+      </c>
+      <c r="E237" t="s">
+        <v>32</v>
+      </c>
+      <c r="F237" t="s">
+        <v>32</v>
+      </c>
+      <c r="G237" t="s">
+        <v>32</v>
+      </c>
+      <c r="H237" t="s">
+        <v>32</v>
+      </c>
+      <c r="I237" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A238" s="5">
+        <v>1010034</v>
+      </c>
+      <c r="B238" s="5">
+        <v>101</v>
+      </c>
+      <c r="C238" s="5">
+        <v>34</v>
+      </c>
+      <c r="D238" t="s">
+        <v>32</v>
+      </c>
+      <c r="E238" t="s">
+        <v>32</v>
+      </c>
+      <c r="F238" t="s">
+        <v>32</v>
+      </c>
+      <c r="G238" t="s">
+        <v>32</v>
+      </c>
+      <c r="H238" t="s">
+        <v>32</v>
+      </c>
+      <c r="I238" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A239" s="5">
+        <v>1010035</v>
+      </c>
+      <c r="B239" s="5">
+        <v>101</v>
+      </c>
+      <c r="C239" s="5">
+        <v>35</v>
+      </c>
+      <c r="D239" t="s">
+        <v>32</v>
+      </c>
+      <c r="E239" t="s">
+        <v>32</v>
+      </c>
+      <c r="F239" t="s">
+        <v>32</v>
+      </c>
+      <c r="G239" t="s">
+        <v>32</v>
+      </c>
+      <c r="H239" t="s">
+        <v>32</v>
+      </c>
+      <c r="I239" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A240" s="5">
+        <v>1010036</v>
+      </c>
+      <c r="B240" s="5">
+        <v>101</v>
+      </c>
+      <c r="C240" s="5">
+        <v>36</v>
+      </c>
+      <c r="D240" t="s">
+        <v>32</v>
+      </c>
+      <c r="E240" t="s">
+        <v>32</v>
+      </c>
+      <c r="F240" t="s">
+        <v>32</v>
+      </c>
+      <c r="G240" t="s">
+        <v>32</v>
+      </c>
+      <c r="H240" t="s">
+        <v>32</v>
+      </c>
+      <c r="I240" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A241" s="5">
+        <v>1010037</v>
+      </c>
+      <c r="B241" s="5">
+        <v>101</v>
+      </c>
+      <c r="C241" s="5">
+        <v>37</v>
+      </c>
+      <c r="D241" t="s">
+        <v>32</v>
+      </c>
+      <c r="E241" t="s">
+        <v>32</v>
+      </c>
+      <c r="F241" t="s">
+        <v>32</v>
+      </c>
+      <c r="G241" t="s">
+        <v>32</v>
+      </c>
+      <c r="H241" t="s">
+        <v>32</v>
+      </c>
+      <c r="I241" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A242" s="5">
+        <v>1010038</v>
+      </c>
+      <c r="B242" s="5">
+        <v>101</v>
+      </c>
+      <c r="C242" s="5">
+        <v>38</v>
+      </c>
+      <c r="D242" t="s">
+        <v>32</v>
+      </c>
+      <c r="E242" t="s">
+        <v>32</v>
+      </c>
+      <c r="F242" t="s">
+        <v>32</v>
+      </c>
+      <c r="G242" t="s">
+        <v>32</v>
+      </c>
+      <c r="H242" t="s">
+        <v>32</v>
+      </c>
+      <c r="I242" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A243" s="5">
+        <v>1010039</v>
+      </c>
+      <c r="B243" s="5">
+        <v>101</v>
+      </c>
+      <c r="C243" s="5">
+        <v>39</v>
+      </c>
+      <c r="D243" t="s">
+        <v>32</v>
+      </c>
+      <c r="E243" t="s">
+        <v>32</v>
+      </c>
+      <c r="F243" t="s">
+        <v>32</v>
+      </c>
+      <c r="G243" t="s">
+        <v>32</v>
+      </c>
+      <c r="H243" t="s">
+        <v>32</v>
+      </c>
+      <c r="I243" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A244" s="5">
+        <v>1010040</v>
+      </c>
+      <c r="B244" s="5">
+        <v>101</v>
+      </c>
+      <c r="C244" s="5">
+        <v>40</v>
+      </c>
+      <c r="D244" t="s">
+        <v>32</v>
+      </c>
+      <c r="E244" t="s">
+        <v>32</v>
+      </c>
+      <c r="F244" t="s">
+        <v>32</v>
+      </c>
+      <c r="G244" t="s">
+        <v>32</v>
+      </c>
+      <c r="H244" t="s">
+        <v>32</v>
+      </c>
+      <c r="I244" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A245" s="5">
+        <v>1010041</v>
+      </c>
+      <c r="B245" s="5">
+        <v>101</v>
+      </c>
+      <c r="C245" s="5">
+        <v>41</v>
+      </c>
+      <c r="D245" t="s">
+        <v>32</v>
+      </c>
+      <c r="E245" t="s">
+        <v>32</v>
+      </c>
+      <c r="F245" t="s">
+        <v>32</v>
+      </c>
+      <c r="G245" t="s">
+        <v>32</v>
+      </c>
+      <c r="H245" t="s">
+        <v>32</v>
+      </c>
+      <c r="I245" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A246" s="5">
+        <v>1010042</v>
+      </c>
+      <c r="B246" s="5">
+        <v>101</v>
+      </c>
+      <c r="C246" s="5">
+        <v>42</v>
+      </c>
+      <c r="D246" t="s">
+        <v>32</v>
+      </c>
+      <c r="E246" t="s">
+        <v>32</v>
+      </c>
+      <c r="F246" t="s">
+        <v>32</v>
+      </c>
+      <c r="G246" t="s">
+        <v>32</v>
+      </c>
+      <c r="H246" t="s">
+        <v>32</v>
+      </c>
+      <c r="I246" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A247" s="5">
+        <v>1010043</v>
+      </c>
+      <c r="B247" s="5">
+        <v>101</v>
+      </c>
+      <c r="C247" s="5">
+        <v>43</v>
+      </c>
+      <c r="D247" t="s">
+        <v>32</v>
+      </c>
+      <c r="E247" t="s">
+        <v>32</v>
+      </c>
+      <c r="F247" t="s">
+        <v>32</v>
+      </c>
+      <c r="G247" t="s">
+        <v>32</v>
+      </c>
+      <c r="H247" t="s">
+        <v>32</v>
+      </c>
+      <c r="I247" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A248" s="5">
+        <v>1010044</v>
+      </c>
+      <c r="B248" s="5">
+        <v>101</v>
+      </c>
+      <c r="C248" s="5">
+        <v>44</v>
+      </c>
+      <c r="D248" t="s">
+        <v>32</v>
+      </c>
+      <c r="E248" t="s">
+        <v>32</v>
+      </c>
+      <c r="F248" t="s">
+        <v>32</v>
+      </c>
+      <c r="G248" t="s">
+        <v>32</v>
+      </c>
+      <c r="H248" t="s">
+        <v>32</v>
+      </c>
+      <c r="I248" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A249" s="5">
+        <v>1010045</v>
+      </c>
+      <c r="B249" s="5">
+        <v>101</v>
+      </c>
+      <c r="C249" s="5">
+        <v>45</v>
+      </c>
+      <c r="D249" t="s">
+        <v>32</v>
+      </c>
+      <c r="E249" t="s">
+        <v>32</v>
+      </c>
+      <c r="F249" t="s">
+        <v>32</v>
+      </c>
+      <c r="G249" t="s">
+        <v>32</v>
+      </c>
+      <c r="H249" t="s">
+        <v>32</v>
+      </c>
+      <c r="I249" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A250" s="5">
+        <v>1010046</v>
+      </c>
+      <c r="B250" s="5">
+        <v>101</v>
+      </c>
+      <c r="C250" s="5">
+        <v>46</v>
+      </c>
+      <c r="D250" t="s">
+        <v>32</v>
+      </c>
+      <c r="E250" t="s">
+        <v>32</v>
+      </c>
+      <c r="F250" t="s">
+        <v>32</v>
+      </c>
+      <c r="G250" t="s">
+        <v>32</v>
+      </c>
+      <c r="H250" t="s">
+        <v>32</v>
+      </c>
+      <c r="I250" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A251" s="5">
+        <v>1010047</v>
+      </c>
+      <c r="B251" s="5">
+        <v>101</v>
+      </c>
+      <c r="C251" s="5">
+        <v>47</v>
+      </c>
+      <c r="D251" t="s">
+        <v>32</v>
+      </c>
+      <c r="E251" t="s">
+        <v>32</v>
+      </c>
+      <c r="F251" t="s">
+        <v>32</v>
+      </c>
+      <c r="G251" t="s">
+        <v>32</v>
+      </c>
+      <c r="H251" t="s">
+        <v>32</v>
+      </c>
+      <c r="I251" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A252" s="5">
+        <v>1010048</v>
+      </c>
+      <c r="B252" s="5">
+        <v>101</v>
+      </c>
+      <c r="C252" s="5">
+        <v>48</v>
+      </c>
+      <c r="D252" t="s">
+        <v>32</v>
+      </c>
+      <c r="E252" t="s">
+        <v>32</v>
+      </c>
+      <c r="F252" t="s">
+        <v>32</v>
+      </c>
+      <c r="G252" t="s">
+        <v>32</v>
+      </c>
+      <c r="H252" t="s">
+        <v>32</v>
+      </c>
+      <c r="I252" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A253" s="5">
+        <v>1010049</v>
+      </c>
+      <c r="B253" s="5">
+        <v>101</v>
+      </c>
+      <c r="C253" s="5">
+        <v>49</v>
+      </c>
+      <c r="D253" t="s">
+        <v>32</v>
+      </c>
+      <c r="E253" t="s">
+        <v>32</v>
+      </c>
+      <c r="F253" t="s">
+        <v>32</v>
+      </c>
+      <c r="G253" t="s">
+        <v>32</v>
+      </c>
+      <c r="H253" t="s">
+        <v>32</v>
+      </c>
+      <c r="I253" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A254" s="5">
+        <v>1010050</v>
+      </c>
+      <c r="B254" s="5">
+        <v>101</v>
+      </c>
+      <c r="C254" s="5">
+        <v>50</v>
+      </c>
+      <c r="D254" t="s">
+        <v>32</v>
+      </c>
+      <c r="E254" t="s">
+        <v>32</v>
+      </c>
+      <c r="F254" t="s">
+        <v>32</v>
+      </c>
+      <c r="G254" t="s">
+        <v>32</v>
+      </c>
+      <c r="H254" t="s">
+        <v>32</v>
+      </c>
+      <c r="I254" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A255" s="5">
+        <v>1010051</v>
+      </c>
+      <c r="B255" s="5">
+        <v>101</v>
+      </c>
+      <c r="C255" s="5">
+        <v>51</v>
+      </c>
+      <c r="D255" t="s">
+        <v>32</v>
+      </c>
+      <c r="E255" t="s">
+        <v>32</v>
+      </c>
+      <c r="F255" t="s">
+        <v>32</v>
+      </c>
+      <c r="G255" t="s">
+        <v>32</v>
+      </c>
+      <c r="H255" t="s">
+        <v>32</v>
+      </c>
+      <c r="I255" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A256" s="5">
+        <v>1010052</v>
+      </c>
+      <c r="B256" s="5">
+        <v>101</v>
+      </c>
+      <c r="C256" s="5">
+        <v>52</v>
+      </c>
+      <c r="D256" t="s">
+        <v>32</v>
+      </c>
+      <c r="E256" t="s">
+        <v>32</v>
+      </c>
+      <c r="F256" t="s">
+        <v>32</v>
+      </c>
+      <c r="G256" t="s">
+        <v>32</v>
+      </c>
+      <c r="H256" t="s">
+        <v>32</v>
+      </c>
+      <c r="I256" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A257" s="5">
+        <v>1010053</v>
+      </c>
+      <c r="B257" s="5">
+        <v>101</v>
+      </c>
+      <c r="C257" s="5">
+        <v>53</v>
+      </c>
+      <c r="D257" t="s">
+        <v>32</v>
+      </c>
+      <c r="E257" t="s">
+        <v>32</v>
+      </c>
+      <c r="F257" t="s">
+        <v>32</v>
+      </c>
+      <c r="G257" t="s">
+        <v>32</v>
+      </c>
+      <c r="H257" t="s">
+        <v>32</v>
+      </c>
+      <c r="I257" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A258" s="5">
+        <v>1010054</v>
+      </c>
+      <c r="B258" s="5">
+        <v>101</v>
+      </c>
+      <c r="C258" s="5">
+        <v>54</v>
+      </c>
+      <c r="D258" t="s">
+        <v>32</v>
+      </c>
+      <c r="E258" t="s">
+        <v>32</v>
+      </c>
+      <c r="F258" t="s">
+        <v>32</v>
+      </c>
+      <c r="G258" t="s">
+        <v>32</v>
+      </c>
+      <c r="H258" t="s">
+        <v>32</v>
+      </c>
+      <c r="I258" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A259" s="5">
+        <v>1010055</v>
+      </c>
+      <c r="B259" s="5">
+        <v>101</v>
+      </c>
+      <c r="C259" s="5">
+        <v>55</v>
+      </c>
+      <c r="D259" t="s">
+        <v>32</v>
+      </c>
+      <c r="E259" t="s">
+        <v>32</v>
+      </c>
+      <c r="F259" t="s">
+        <v>32</v>
+      </c>
+      <c r="G259" t="s">
+        <v>32</v>
+      </c>
+      <c r="H259" t="s">
+        <v>32</v>
+      </c>
+      <c r="I259" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A260" s="5">
+        <v>1010056</v>
+      </c>
+      <c r="B260" s="5">
+        <v>101</v>
+      </c>
+      <c r="C260" s="5">
+        <v>56</v>
+      </c>
+      <c r="D260" t="s">
+        <v>32</v>
+      </c>
+      <c r="E260" t="s">
+        <v>32</v>
+      </c>
+      <c r="F260" t="s">
+        <v>32</v>
+      </c>
+      <c r="G260" t="s">
+        <v>32</v>
+      </c>
+      <c r="H260" t="s">
+        <v>32</v>
+      </c>
+      <c r="I260" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A261" s="5">
+        <v>1010057</v>
+      </c>
+      <c r="B261" s="5">
+        <v>101</v>
+      </c>
+      <c r="C261" s="5">
+        <v>57</v>
+      </c>
+      <c r="D261" t="s">
+        <v>32</v>
+      </c>
+      <c r="E261" t="s">
+        <v>32</v>
+      </c>
+      <c r="F261" t="s">
+        <v>32</v>
+      </c>
+      <c r="G261" t="s">
+        <v>32</v>
+      </c>
+      <c r="H261" t="s">
+        <v>32</v>
+      </c>
+      <c r="I261" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A262" s="5">
+        <v>1010058</v>
+      </c>
+      <c r="B262" s="5">
+        <v>101</v>
+      </c>
+      <c r="C262" s="5">
+        <v>58</v>
+      </c>
+      <c r="D262" t="s">
+        <v>32</v>
+      </c>
+      <c r="E262" t="s">
+        <v>32</v>
+      </c>
+      <c r="F262" t="s">
+        <v>32</v>
+      </c>
+      <c r="G262" t="s">
+        <v>32</v>
+      </c>
+      <c r="H262" t="s">
+        <v>32</v>
+      </c>
+      <c r="I262" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A263" s="5">
+        <v>1010059</v>
+      </c>
+      <c r="B263" s="5">
+        <v>101</v>
+      </c>
+      <c r="C263" s="5">
+        <v>59</v>
+      </c>
+      <c r="D263" t="s">
+        <v>32</v>
+      </c>
+      <c r="E263" t="s">
+        <v>32</v>
+      </c>
+      <c r="F263" t="s">
+        <v>32</v>
+      </c>
+      <c r="G263" t="s">
+        <v>32</v>
+      </c>
+      <c r="H263" t="s">
+        <v>32</v>
+      </c>
+      <c r="I263" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A264" s="5">
+        <v>1010060</v>
+      </c>
+      <c r="B264" s="5">
+        <v>101</v>
+      </c>
+      <c r="C264" s="5">
+        <v>60</v>
+      </c>
+      <c r="D264" t="s">
+        <v>32</v>
+      </c>
+      <c r="E264" t="s">
+        <v>32</v>
+      </c>
+      <c r="F264" t="s">
+        <v>32</v>
+      </c>
+      <c r="G264" t="s">
+        <v>32</v>
+      </c>
+      <c r="H264" t="s">
+        <v>32</v>
+      </c>
+      <c r="I264" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F424D6A-2D65-480F-A7EA-2D33E282B863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42672B62-EF56-4427-9D83-FBAD6DA40F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="35">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,6 +159,10 @@
   </si>
   <si>
     <t>201:100_202:100_203:100_204:100_205:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>301:100_302:100_303:100_304:100_305:100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -535,7 +539,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I264"/>
+  <dimension ref="A1:I324"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" style="5" bestFit="1" customWidth="1"/>
@@ -8177,6 +8181,1746 @@
         <v>32</v>
       </c>
     </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A265" s="5">
+        <v>1020001</v>
+      </c>
+      <c r="B265" s="5">
+        <v>102</v>
+      </c>
+      <c r="C265" s="5">
+        <v>1</v>
+      </c>
+      <c r="D265" t="s">
+        <v>34</v>
+      </c>
+      <c r="E265" t="s">
+        <v>34</v>
+      </c>
+      <c r="F265" t="s">
+        <v>34</v>
+      </c>
+      <c r="G265" t="s">
+        <v>34</v>
+      </c>
+      <c r="H265" t="s">
+        <v>34</v>
+      </c>
+      <c r="I265" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A266" s="5">
+        <v>1020002</v>
+      </c>
+      <c r="B266" s="5">
+        <v>102</v>
+      </c>
+      <c r="C266" s="5">
+        <v>2</v>
+      </c>
+      <c r="D266" t="s">
+        <v>34</v>
+      </c>
+      <c r="E266" t="s">
+        <v>34</v>
+      </c>
+      <c r="F266" t="s">
+        <v>34</v>
+      </c>
+      <c r="G266" t="s">
+        <v>34</v>
+      </c>
+      <c r="H266" t="s">
+        <v>34</v>
+      </c>
+      <c r="I266" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A267" s="5">
+        <v>1020003</v>
+      </c>
+      <c r="B267" s="5">
+        <v>102</v>
+      </c>
+      <c r="C267" s="5">
+        <v>3</v>
+      </c>
+      <c r="D267" t="s">
+        <v>34</v>
+      </c>
+      <c r="E267" t="s">
+        <v>34</v>
+      </c>
+      <c r="F267" t="s">
+        <v>34</v>
+      </c>
+      <c r="G267" t="s">
+        <v>34</v>
+      </c>
+      <c r="H267" t="s">
+        <v>34</v>
+      </c>
+      <c r="I267" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A268" s="5">
+        <v>1020004</v>
+      </c>
+      <c r="B268" s="5">
+        <v>102</v>
+      </c>
+      <c r="C268" s="5">
+        <v>4</v>
+      </c>
+      <c r="D268" t="s">
+        <v>34</v>
+      </c>
+      <c r="E268" t="s">
+        <v>34</v>
+      </c>
+      <c r="F268" t="s">
+        <v>34</v>
+      </c>
+      <c r="G268" t="s">
+        <v>34</v>
+      </c>
+      <c r="H268" t="s">
+        <v>34</v>
+      </c>
+      <c r="I268" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A269" s="5">
+        <v>1020005</v>
+      </c>
+      <c r="B269" s="5">
+        <v>102</v>
+      </c>
+      <c r="C269" s="5">
+        <v>5</v>
+      </c>
+      <c r="D269" t="s">
+        <v>34</v>
+      </c>
+      <c r="E269" t="s">
+        <v>34</v>
+      </c>
+      <c r="F269" t="s">
+        <v>34</v>
+      </c>
+      <c r="G269" t="s">
+        <v>34</v>
+      </c>
+      <c r="H269" t="s">
+        <v>34</v>
+      </c>
+      <c r="I269" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A270" s="5">
+        <v>1020006</v>
+      </c>
+      <c r="B270" s="5">
+        <v>102</v>
+      </c>
+      <c r="C270" s="5">
+        <v>6</v>
+      </c>
+      <c r="D270" t="s">
+        <v>34</v>
+      </c>
+      <c r="E270" t="s">
+        <v>34</v>
+      </c>
+      <c r="F270" t="s">
+        <v>34</v>
+      </c>
+      <c r="G270" t="s">
+        <v>34</v>
+      </c>
+      <c r="H270" t="s">
+        <v>34</v>
+      </c>
+      <c r="I270" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A271" s="5">
+        <v>1020007</v>
+      </c>
+      <c r="B271" s="5">
+        <v>102</v>
+      </c>
+      <c r="C271" s="5">
+        <v>7</v>
+      </c>
+      <c r="D271" t="s">
+        <v>34</v>
+      </c>
+      <c r="E271" t="s">
+        <v>34</v>
+      </c>
+      <c r="F271" t="s">
+        <v>34</v>
+      </c>
+      <c r="G271" t="s">
+        <v>34</v>
+      </c>
+      <c r="H271" t="s">
+        <v>34</v>
+      </c>
+      <c r="I271" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A272" s="5">
+        <v>1020008</v>
+      </c>
+      <c r="B272" s="5">
+        <v>102</v>
+      </c>
+      <c r="C272" s="5">
+        <v>8</v>
+      </c>
+      <c r="D272" t="s">
+        <v>34</v>
+      </c>
+      <c r="E272" t="s">
+        <v>34</v>
+      </c>
+      <c r="F272" t="s">
+        <v>34</v>
+      </c>
+      <c r="G272" t="s">
+        <v>34</v>
+      </c>
+      <c r="H272" t="s">
+        <v>34</v>
+      </c>
+      <c r="I272" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A273" s="5">
+        <v>1020009</v>
+      </c>
+      <c r="B273" s="5">
+        <v>102</v>
+      </c>
+      <c r="C273" s="5">
+        <v>9</v>
+      </c>
+      <c r="D273" t="s">
+        <v>34</v>
+      </c>
+      <c r="E273" t="s">
+        <v>34</v>
+      </c>
+      <c r="F273" t="s">
+        <v>34</v>
+      </c>
+      <c r="G273" t="s">
+        <v>34</v>
+      </c>
+      <c r="H273" t="s">
+        <v>34</v>
+      </c>
+      <c r="I273" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A274" s="5">
+        <v>1020010</v>
+      </c>
+      <c r="B274" s="5">
+        <v>102</v>
+      </c>
+      <c r="C274" s="5">
+        <v>10</v>
+      </c>
+      <c r="D274" t="s">
+        <v>34</v>
+      </c>
+      <c r="E274" t="s">
+        <v>34</v>
+      </c>
+      <c r="F274" t="s">
+        <v>34</v>
+      </c>
+      <c r="G274" t="s">
+        <v>34</v>
+      </c>
+      <c r="H274" t="s">
+        <v>34</v>
+      </c>
+      <c r="I274" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A275" s="5">
+        <v>1020011</v>
+      </c>
+      <c r="B275" s="5">
+        <v>102</v>
+      </c>
+      <c r="C275" s="5">
+        <v>11</v>
+      </c>
+      <c r="D275" t="s">
+        <v>34</v>
+      </c>
+      <c r="E275" t="s">
+        <v>34</v>
+      </c>
+      <c r="F275" t="s">
+        <v>34</v>
+      </c>
+      <c r="G275" t="s">
+        <v>34</v>
+      </c>
+      <c r="H275" t="s">
+        <v>34</v>
+      </c>
+      <c r="I275" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A276" s="5">
+        <v>1020012</v>
+      </c>
+      <c r="B276" s="5">
+        <v>102</v>
+      </c>
+      <c r="C276" s="5">
+        <v>12</v>
+      </c>
+      <c r="D276" t="s">
+        <v>34</v>
+      </c>
+      <c r="E276" t="s">
+        <v>34</v>
+      </c>
+      <c r="F276" t="s">
+        <v>34</v>
+      </c>
+      <c r="G276" t="s">
+        <v>34</v>
+      </c>
+      <c r="H276" t="s">
+        <v>34</v>
+      </c>
+      <c r="I276" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A277" s="5">
+        <v>1020013</v>
+      </c>
+      <c r="B277" s="5">
+        <v>102</v>
+      </c>
+      <c r="C277" s="5">
+        <v>13</v>
+      </c>
+      <c r="D277" t="s">
+        <v>34</v>
+      </c>
+      <c r="E277" t="s">
+        <v>34</v>
+      </c>
+      <c r="F277" t="s">
+        <v>34</v>
+      </c>
+      <c r="G277" t="s">
+        <v>34</v>
+      </c>
+      <c r="H277" t="s">
+        <v>34</v>
+      </c>
+      <c r="I277" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A278" s="5">
+        <v>1020014</v>
+      </c>
+      <c r="B278" s="5">
+        <v>102</v>
+      </c>
+      <c r="C278" s="5">
+        <v>14</v>
+      </c>
+      <c r="D278" t="s">
+        <v>34</v>
+      </c>
+      <c r="E278" t="s">
+        <v>34</v>
+      </c>
+      <c r="F278" t="s">
+        <v>34</v>
+      </c>
+      <c r="G278" t="s">
+        <v>34</v>
+      </c>
+      <c r="H278" t="s">
+        <v>34</v>
+      </c>
+      <c r="I278" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A279" s="5">
+        <v>1020015</v>
+      </c>
+      <c r="B279" s="5">
+        <v>102</v>
+      </c>
+      <c r="C279" s="5">
+        <v>15</v>
+      </c>
+      <c r="D279" t="s">
+        <v>34</v>
+      </c>
+      <c r="E279" t="s">
+        <v>34</v>
+      </c>
+      <c r="F279" t="s">
+        <v>34</v>
+      </c>
+      <c r="G279" t="s">
+        <v>34</v>
+      </c>
+      <c r="H279" t="s">
+        <v>34</v>
+      </c>
+      <c r="I279" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A280" s="5">
+        <v>1020016</v>
+      </c>
+      <c r="B280" s="5">
+        <v>102</v>
+      </c>
+      <c r="C280" s="5">
+        <v>16</v>
+      </c>
+      <c r="D280" t="s">
+        <v>34</v>
+      </c>
+      <c r="E280" t="s">
+        <v>34</v>
+      </c>
+      <c r="F280" t="s">
+        <v>34</v>
+      </c>
+      <c r="G280" t="s">
+        <v>34</v>
+      </c>
+      <c r="H280" t="s">
+        <v>34</v>
+      </c>
+      <c r="I280" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A281" s="5">
+        <v>1020017</v>
+      </c>
+      <c r="B281" s="5">
+        <v>102</v>
+      </c>
+      <c r="C281" s="5">
+        <v>17</v>
+      </c>
+      <c r="D281" t="s">
+        <v>34</v>
+      </c>
+      <c r="E281" t="s">
+        <v>34</v>
+      </c>
+      <c r="F281" t="s">
+        <v>34</v>
+      </c>
+      <c r="G281" t="s">
+        <v>34</v>
+      </c>
+      <c r="H281" t="s">
+        <v>34</v>
+      </c>
+      <c r="I281" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A282" s="5">
+        <v>1020018</v>
+      </c>
+      <c r="B282" s="5">
+        <v>102</v>
+      </c>
+      <c r="C282" s="5">
+        <v>18</v>
+      </c>
+      <c r="D282" t="s">
+        <v>34</v>
+      </c>
+      <c r="E282" t="s">
+        <v>34</v>
+      </c>
+      <c r="F282" t="s">
+        <v>34</v>
+      </c>
+      <c r="G282" t="s">
+        <v>34</v>
+      </c>
+      <c r="H282" t="s">
+        <v>34</v>
+      </c>
+      <c r="I282" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A283" s="5">
+        <v>1020019</v>
+      </c>
+      <c r="B283" s="5">
+        <v>102</v>
+      </c>
+      <c r="C283" s="5">
+        <v>19</v>
+      </c>
+      <c r="D283" t="s">
+        <v>34</v>
+      </c>
+      <c r="E283" t="s">
+        <v>34</v>
+      </c>
+      <c r="F283" t="s">
+        <v>34</v>
+      </c>
+      <c r="G283" t="s">
+        <v>34</v>
+      </c>
+      <c r="H283" t="s">
+        <v>34</v>
+      </c>
+      <c r="I283" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A284" s="5">
+        <v>1020020</v>
+      </c>
+      <c r="B284" s="5">
+        <v>102</v>
+      </c>
+      <c r="C284" s="5">
+        <v>20</v>
+      </c>
+      <c r="D284" t="s">
+        <v>34</v>
+      </c>
+      <c r="E284" t="s">
+        <v>34</v>
+      </c>
+      <c r="F284" t="s">
+        <v>34</v>
+      </c>
+      <c r="G284" t="s">
+        <v>34</v>
+      </c>
+      <c r="H284" t="s">
+        <v>34</v>
+      </c>
+      <c r="I284" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A285" s="5">
+        <v>1020021</v>
+      </c>
+      <c r="B285" s="5">
+        <v>102</v>
+      </c>
+      <c r="C285" s="5">
+        <v>21</v>
+      </c>
+      <c r="D285" t="s">
+        <v>34</v>
+      </c>
+      <c r="E285" t="s">
+        <v>34</v>
+      </c>
+      <c r="F285" t="s">
+        <v>34</v>
+      </c>
+      <c r="G285" t="s">
+        <v>34</v>
+      </c>
+      <c r="H285" t="s">
+        <v>34</v>
+      </c>
+      <c r="I285" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A286" s="5">
+        <v>1020022</v>
+      </c>
+      <c r="B286" s="5">
+        <v>102</v>
+      </c>
+      <c r="C286" s="5">
+        <v>22</v>
+      </c>
+      <c r="D286" t="s">
+        <v>34</v>
+      </c>
+      <c r="E286" t="s">
+        <v>34</v>
+      </c>
+      <c r="F286" t="s">
+        <v>34</v>
+      </c>
+      <c r="G286" t="s">
+        <v>34</v>
+      </c>
+      <c r="H286" t="s">
+        <v>34</v>
+      </c>
+      <c r="I286" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A287" s="5">
+        <v>1020023</v>
+      </c>
+      <c r="B287" s="5">
+        <v>102</v>
+      </c>
+      <c r="C287" s="5">
+        <v>23</v>
+      </c>
+      <c r="D287" t="s">
+        <v>34</v>
+      </c>
+      <c r="E287" t="s">
+        <v>34</v>
+      </c>
+      <c r="F287" t="s">
+        <v>34</v>
+      </c>
+      <c r="G287" t="s">
+        <v>34</v>
+      </c>
+      <c r="H287" t="s">
+        <v>34</v>
+      </c>
+      <c r="I287" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A288" s="5">
+        <v>1020024</v>
+      </c>
+      <c r="B288" s="5">
+        <v>102</v>
+      </c>
+      <c r="C288" s="5">
+        <v>24</v>
+      </c>
+      <c r="D288" t="s">
+        <v>34</v>
+      </c>
+      <c r="E288" t="s">
+        <v>34</v>
+      </c>
+      <c r="F288" t="s">
+        <v>34</v>
+      </c>
+      <c r="G288" t="s">
+        <v>34</v>
+      </c>
+      <c r="H288" t="s">
+        <v>34</v>
+      </c>
+      <c r="I288" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A289" s="5">
+        <v>1020025</v>
+      </c>
+      <c r="B289" s="5">
+        <v>102</v>
+      </c>
+      <c r="C289" s="5">
+        <v>25</v>
+      </c>
+      <c r="D289" t="s">
+        <v>34</v>
+      </c>
+      <c r="E289" t="s">
+        <v>34</v>
+      </c>
+      <c r="F289" t="s">
+        <v>34</v>
+      </c>
+      <c r="G289" t="s">
+        <v>34</v>
+      </c>
+      <c r="H289" t="s">
+        <v>34</v>
+      </c>
+      <c r="I289" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A290" s="5">
+        <v>1020026</v>
+      </c>
+      <c r="B290" s="5">
+        <v>102</v>
+      </c>
+      <c r="C290" s="5">
+        <v>26</v>
+      </c>
+      <c r="D290" t="s">
+        <v>34</v>
+      </c>
+      <c r="E290" t="s">
+        <v>34</v>
+      </c>
+      <c r="F290" t="s">
+        <v>34</v>
+      </c>
+      <c r="G290" t="s">
+        <v>34</v>
+      </c>
+      <c r="H290" t="s">
+        <v>34</v>
+      </c>
+      <c r="I290" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A291" s="5">
+        <v>1020027</v>
+      </c>
+      <c r="B291" s="5">
+        <v>102</v>
+      </c>
+      <c r="C291" s="5">
+        <v>27</v>
+      </c>
+      <c r="D291" t="s">
+        <v>34</v>
+      </c>
+      <c r="E291" t="s">
+        <v>34</v>
+      </c>
+      <c r="F291" t="s">
+        <v>34</v>
+      </c>
+      <c r="G291" t="s">
+        <v>34</v>
+      </c>
+      <c r="H291" t="s">
+        <v>34</v>
+      </c>
+      <c r="I291" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A292" s="5">
+        <v>1020028</v>
+      </c>
+      <c r="B292" s="5">
+        <v>102</v>
+      </c>
+      <c r="C292" s="5">
+        <v>28</v>
+      </c>
+      <c r="D292" t="s">
+        <v>34</v>
+      </c>
+      <c r="E292" t="s">
+        <v>34</v>
+      </c>
+      <c r="F292" t="s">
+        <v>34</v>
+      </c>
+      <c r="G292" t="s">
+        <v>34</v>
+      </c>
+      <c r="H292" t="s">
+        <v>34</v>
+      </c>
+      <c r="I292" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A293" s="5">
+        <v>1020029</v>
+      </c>
+      <c r="B293" s="5">
+        <v>102</v>
+      </c>
+      <c r="C293" s="5">
+        <v>29</v>
+      </c>
+      <c r="D293" t="s">
+        <v>34</v>
+      </c>
+      <c r="E293" t="s">
+        <v>34</v>
+      </c>
+      <c r="F293" t="s">
+        <v>34</v>
+      </c>
+      <c r="G293" t="s">
+        <v>34</v>
+      </c>
+      <c r="H293" t="s">
+        <v>34</v>
+      </c>
+      <c r="I293" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A294" s="5">
+        <v>1020030</v>
+      </c>
+      <c r="B294" s="5">
+        <v>102</v>
+      </c>
+      <c r="C294" s="5">
+        <v>30</v>
+      </c>
+      <c r="D294" t="s">
+        <v>34</v>
+      </c>
+      <c r="E294" t="s">
+        <v>34</v>
+      </c>
+      <c r="F294" t="s">
+        <v>34</v>
+      </c>
+      <c r="G294" t="s">
+        <v>34</v>
+      </c>
+      <c r="H294" t="s">
+        <v>34</v>
+      </c>
+      <c r="I294" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A295" s="5">
+        <v>1020031</v>
+      </c>
+      <c r="B295" s="5">
+        <v>102</v>
+      </c>
+      <c r="C295" s="5">
+        <v>31</v>
+      </c>
+      <c r="D295" t="s">
+        <v>34</v>
+      </c>
+      <c r="E295" t="s">
+        <v>34</v>
+      </c>
+      <c r="F295" t="s">
+        <v>34</v>
+      </c>
+      <c r="G295" t="s">
+        <v>34</v>
+      </c>
+      <c r="H295" t="s">
+        <v>34</v>
+      </c>
+      <c r="I295" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A296" s="5">
+        <v>1020032</v>
+      </c>
+      <c r="B296" s="5">
+        <v>102</v>
+      </c>
+      <c r="C296" s="5">
+        <v>32</v>
+      </c>
+      <c r="D296" t="s">
+        <v>34</v>
+      </c>
+      <c r="E296" t="s">
+        <v>34</v>
+      </c>
+      <c r="F296" t="s">
+        <v>34</v>
+      </c>
+      <c r="G296" t="s">
+        <v>34</v>
+      </c>
+      <c r="H296" t="s">
+        <v>34</v>
+      </c>
+      <c r="I296" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A297" s="5">
+        <v>1020033</v>
+      </c>
+      <c r="B297" s="5">
+        <v>102</v>
+      </c>
+      <c r="C297" s="5">
+        <v>33</v>
+      </c>
+      <c r="D297" t="s">
+        <v>34</v>
+      </c>
+      <c r="E297" t="s">
+        <v>34</v>
+      </c>
+      <c r="F297" t="s">
+        <v>34</v>
+      </c>
+      <c r="G297" t="s">
+        <v>34</v>
+      </c>
+      <c r="H297" t="s">
+        <v>34</v>
+      </c>
+      <c r="I297" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A298" s="5">
+        <v>1020034</v>
+      </c>
+      <c r="B298" s="5">
+        <v>102</v>
+      </c>
+      <c r="C298" s="5">
+        <v>34</v>
+      </c>
+      <c r="D298" t="s">
+        <v>34</v>
+      </c>
+      <c r="E298" t="s">
+        <v>34</v>
+      </c>
+      <c r="F298" t="s">
+        <v>34</v>
+      </c>
+      <c r="G298" t="s">
+        <v>34</v>
+      </c>
+      <c r="H298" t="s">
+        <v>34</v>
+      </c>
+      <c r="I298" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A299" s="5">
+        <v>1020035</v>
+      </c>
+      <c r="B299" s="5">
+        <v>102</v>
+      </c>
+      <c r="C299" s="5">
+        <v>35</v>
+      </c>
+      <c r="D299" t="s">
+        <v>34</v>
+      </c>
+      <c r="E299" t="s">
+        <v>34</v>
+      </c>
+      <c r="F299" t="s">
+        <v>34</v>
+      </c>
+      <c r="G299" t="s">
+        <v>34</v>
+      </c>
+      <c r="H299" t="s">
+        <v>34</v>
+      </c>
+      <c r="I299" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A300" s="5">
+        <v>1020036</v>
+      </c>
+      <c r="B300" s="5">
+        <v>102</v>
+      </c>
+      <c r="C300" s="5">
+        <v>36</v>
+      </c>
+      <c r="D300" t="s">
+        <v>34</v>
+      </c>
+      <c r="E300" t="s">
+        <v>34</v>
+      </c>
+      <c r="F300" t="s">
+        <v>34</v>
+      </c>
+      <c r="G300" t="s">
+        <v>34</v>
+      </c>
+      <c r="H300" t="s">
+        <v>34</v>
+      </c>
+      <c r="I300" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A301" s="5">
+        <v>1020037</v>
+      </c>
+      <c r="B301" s="5">
+        <v>102</v>
+      </c>
+      <c r="C301" s="5">
+        <v>37</v>
+      </c>
+      <c r="D301" t="s">
+        <v>34</v>
+      </c>
+      <c r="E301" t="s">
+        <v>34</v>
+      </c>
+      <c r="F301" t="s">
+        <v>34</v>
+      </c>
+      <c r="G301" t="s">
+        <v>34</v>
+      </c>
+      <c r="H301" t="s">
+        <v>34</v>
+      </c>
+      <c r="I301" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A302" s="5">
+        <v>1020038</v>
+      </c>
+      <c r="B302" s="5">
+        <v>102</v>
+      </c>
+      <c r="C302" s="5">
+        <v>38</v>
+      </c>
+      <c r="D302" t="s">
+        <v>34</v>
+      </c>
+      <c r="E302" t="s">
+        <v>34</v>
+      </c>
+      <c r="F302" t="s">
+        <v>34</v>
+      </c>
+      <c r="G302" t="s">
+        <v>34</v>
+      </c>
+      <c r="H302" t="s">
+        <v>34</v>
+      </c>
+      <c r="I302" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A303" s="5">
+        <v>1020039</v>
+      </c>
+      <c r="B303" s="5">
+        <v>102</v>
+      </c>
+      <c r="C303" s="5">
+        <v>39</v>
+      </c>
+      <c r="D303" t="s">
+        <v>34</v>
+      </c>
+      <c r="E303" t="s">
+        <v>34</v>
+      </c>
+      <c r="F303" t="s">
+        <v>34</v>
+      </c>
+      <c r="G303" t="s">
+        <v>34</v>
+      </c>
+      <c r="H303" t="s">
+        <v>34</v>
+      </c>
+      <c r="I303" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A304" s="5">
+        <v>1020040</v>
+      </c>
+      <c r="B304" s="5">
+        <v>102</v>
+      </c>
+      <c r="C304" s="5">
+        <v>40</v>
+      </c>
+      <c r="D304" t="s">
+        <v>34</v>
+      </c>
+      <c r="E304" t="s">
+        <v>34</v>
+      </c>
+      <c r="F304" t="s">
+        <v>34</v>
+      </c>
+      <c r="G304" t="s">
+        <v>34</v>
+      </c>
+      <c r="H304" t="s">
+        <v>34</v>
+      </c>
+      <c r="I304" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A305" s="5">
+        <v>1020041</v>
+      </c>
+      <c r="B305" s="5">
+        <v>102</v>
+      </c>
+      <c r="C305" s="5">
+        <v>41</v>
+      </c>
+      <c r="D305" t="s">
+        <v>34</v>
+      </c>
+      <c r="E305" t="s">
+        <v>34</v>
+      </c>
+      <c r="F305" t="s">
+        <v>34</v>
+      </c>
+      <c r="G305" t="s">
+        <v>34</v>
+      </c>
+      <c r="H305" t="s">
+        <v>34</v>
+      </c>
+      <c r="I305" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A306" s="5">
+        <v>1020042</v>
+      </c>
+      <c r="B306" s="5">
+        <v>102</v>
+      </c>
+      <c r="C306" s="5">
+        <v>42</v>
+      </c>
+      <c r="D306" t="s">
+        <v>34</v>
+      </c>
+      <c r="E306" t="s">
+        <v>34</v>
+      </c>
+      <c r="F306" t="s">
+        <v>34</v>
+      </c>
+      <c r="G306" t="s">
+        <v>34</v>
+      </c>
+      <c r="H306" t="s">
+        <v>34</v>
+      </c>
+      <c r="I306" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A307" s="5">
+        <v>1020043</v>
+      </c>
+      <c r="B307" s="5">
+        <v>102</v>
+      </c>
+      <c r="C307" s="5">
+        <v>43</v>
+      </c>
+      <c r="D307" t="s">
+        <v>34</v>
+      </c>
+      <c r="E307" t="s">
+        <v>34</v>
+      </c>
+      <c r="F307" t="s">
+        <v>34</v>
+      </c>
+      <c r="G307" t="s">
+        <v>34</v>
+      </c>
+      <c r="H307" t="s">
+        <v>34</v>
+      </c>
+      <c r="I307" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A308" s="5">
+        <v>1020044</v>
+      </c>
+      <c r="B308" s="5">
+        <v>102</v>
+      </c>
+      <c r="C308" s="5">
+        <v>44</v>
+      </c>
+      <c r="D308" t="s">
+        <v>34</v>
+      </c>
+      <c r="E308" t="s">
+        <v>34</v>
+      </c>
+      <c r="F308" t="s">
+        <v>34</v>
+      </c>
+      <c r="G308" t="s">
+        <v>34</v>
+      </c>
+      <c r="H308" t="s">
+        <v>34</v>
+      </c>
+      <c r="I308" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A309" s="5">
+        <v>1020045</v>
+      </c>
+      <c r="B309" s="5">
+        <v>102</v>
+      </c>
+      <c r="C309" s="5">
+        <v>45</v>
+      </c>
+      <c r="D309" t="s">
+        <v>34</v>
+      </c>
+      <c r="E309" t="s">
+        <v>34</v>
+      </c>
+      <c r="F309" t="s">
+        <v>34</v>
+      </c>
+      <c r="G309" t="s">
+        <v>34</v>
+      </c>
+      <c r="H309" t="s">
+        <v>34</v>
+      </c>
+      <c r="I309" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A310" s="5">
+        <v>1020046</v>
+      </c>
+      <c r="B310" s="5">
+        <v>102</v>
+      </c>
+      <c r="C310" s="5">
+        <v>46</v>
+      </c>
+      <c r="D310" t="s">
+        <v>34</v>
+      </c>
+      <c r="E310" t="s">
+        <v>34</v>
+      </c>
+      <c r="F310" t="s">
+        <v>34</v>
+      </c>
+      <c r="G310" t="s">
+        <v>34</v>
+      </c>
+      <c r="H310" t="s">
+        <v>34</v>
+      </c>
+      <c r="I310" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A311" s="5">
+        <v>1020047</v>
+      </c>
+      <c r="B311" s="5">
+        <v>102</v>
+      </c>
+      <c r="C311" s="5">
+        <v>47</v>
+      </c>
+      <c r="D311" t="s">
+        <v>34</v>
+      </c>
+      <c r="E311" t="s">
+        <v>34</v>
+      </c>
+      <c r="F311" t="s">
+        <v>34</v>
+      </c>
+      <c r="G311" t="s">
+        <v>34</v>
+      </c>
+      <c r="H311" t="s">
+        <v>34</v>
+      </c>
+      <c r="I311" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A312" s="5">
+        <v>1020048</v>
+      </c>
+      <c r="B312" s="5">
+        <v>102</v>
+      </c>
+      <c r="C312" s="5">
+        <v>48</v>
+      </c>
+      <c r="D312" t="s">
+        <v>34</v>
+      </c>
+      <c r="E312" t="s">
+        <v>34</v>
+      </c>
+      <c r="F312" t="s">
+        <v>34</v>
+      </c>
+      <c r="G312" t="s">
+        <v>34</v>
+      </c>
+      <c r="H312" t="s">
+        <v>34</v>
+      </c>
+      <c r="I312" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A313" s="5">
+        <v>1020049</v>
+      </c>
+      <c r="B313" s="5">
+        <v>102</v>
+      </c>
+      <c r="C313" s="5">
+        <v>49</v>
+      </c>
+      <c r="D313" t="s">
+        <v>34</v>
+      </c>
+      <c r="E313" t="s">
+        <v>34</v>
+      </c>
+      <c r="F313" t="s">
+        <v>34</v>
+      </c>
+      <c r="G313" t="s">
+        <v>34</v>
+      </c>
+      <c r="H313" t="s">
+        <v>34</v>
+      </c>
+      <c r="I313" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A314" s="5">
+        <v>1020050</v>
+      </c>
+      <c r="B314" s="5">
+        <v>102</v>
+      </c>
+      <c r="C314" s="5">
+        <v>50</v>
+      </c>
+      <c r="D314" t="s">
+        <v>34</v>
+      </c>
+      <c r="E314" t="s">
+        <v>34</v>
+      </c>
+      <c r="F314" t="s">
+        <v>34</v>
+      </c>
+      <c r="G314" t="s">
+        <v>34</v>
+      </c>
+      <c r="H314" t="s">
+        <v>34</v>
+      </c>
+      <c r="I314" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A315" s="5">
+        <v>1020051</v>
+      </c>
+      <c r="B315" s="5">
+        <v>102</v>
+      </c>
+      <c r="C315" s="5">
+        <v>51</v>
+      </c>
+      <c r="D315" t="s">
+        <v>34</v>
+      </c>
+      <c r="E315" t="s">
+        <v>34</v>
+      </c>
+      <c r="F315" t="s">
+        <v>34</v>
+      </c>
+      <c r="G315" t="s">
+        <v>34</v>
+      </c>
+      <c r="H315" t="s">
+        <v>34</v>
+      </c>
+      <c r="I315" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A316" s="5">
+        <v>1020052</v>
+      </c>
+      <c r="B316" s="5">
+        <v>102</v>
+      </c>
+      <c r="C316" s="5">
+        <v>52</v>
+      </c>
+      <c r="D316" t="s">
+        <v>34</v>
+      </c>
+      <c r="E316" t="s">
+        <v>34</v>
+      </c>
+      <c r="F316" t="s">
+        <v>34</v>
+      </c>
+      <c r="G316" t="s">
+        <v>34</v>
+      </c>
+      <c r="H316" t="s">
+        <v>34</v>
+      </c>
+      <c r="I316" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A317" s="5">
+        <v>1020053</v>
+      </c>
+      <c r="B317" s="5">
+        <v>102</v>
+      </c>
+      <c r="C317" s="5">
+        <v>53</v>
+      </c>
+      <c r="D317" t="s">
+        <v>34</v>
+      </c>
+      <c r="E317" t="s">
+        <v>34</v>
+      </c>
+      <c r="F317" t="s">
+        <v>34</v>
+      </c>
+      <c r="G317" t="s">
+        <v>34</v>
+      </c>
+      <c r="H317" t="s">
+        <v>34</v>
+      </c>
+      <c r="I317" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A318" s="5">
+        <v>1020054</v>
+      </c>
+      <c r="B318" s="5">
+        <v>102</v>
+      </c>
+      <c r="C318" s="5">
+        <v>54</v>
+      </c>
+      <c r="D318" t="s">
+        <v>34</v>
+      </c>
+      <c r="E318" t="s">
+        <v>34</v>
+      </c>
+      <c r="F318" t="s">
+        <v>34</v>
+      </c>
+      <c r="G318" t="s">
+        <v>34</v>
+      </c>
+      <c r="H318" t="s">
+        <v>34</v>
+      </c>
+      <c r="I318" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A319" s="5">
+        <v>1020055</v>
+      </c>
+      <c r="B319" s="5">
+        <v>102</v>
+      </c>
+      <c r="C319" s="5">
+        <v>55</v>
+      </c>
+      <c r="D319" t="s">
+        <v>34</v>
+      </c>
+      <c r="E319" t="s">
+        <v>34</v>
+      </c>
+      <c r="F319" t="s">
+        <v>34</v>
+      </c>
+      <c r="G319" t="s">
+        <v>34</v>
+      </c>
+      <c r="H319" t="s">
+        <v>34</v>
+      </c>
+      <c r="I319" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A320" s="5">
+        <v>1020056</v>
+      </c>
+      <c r="B320" s="5">
+        <v>102</v>
+      </c>
+      <c r="C320" s="5">
+        <v>56</v>
+      </c>
+      <c r="D320" t="s">
+        <v>34</v>
+      </c>
+      <c r="E320" t="s">
+        <v>34</v>
+      </c>
+      <c r="F320" t="s">
+        <v>34</v>
+      </c>
+      <c r="G320" t="s">
+        <v>34</v>
+      </c>
+      <c r="H320" t="s">
+        <v>34</v>
+      </c>
+      <c r="I320" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A321" s="5">
+        <v>1020057</v>
+      </c>
+      <c r="B321" s="5">
+        <v>102</v>
+      </c>
+      <c r="C321" s="5">
+        <v>57</v>
+      </c>
+      <c r="D321" t="s">
+        <v>34</v>
+      </c>
+      <c r="E321" t="s">
+        <v>34</v>
+      </c>
+      <c r="F321" t="s">
+        <v>34</v>
+      </c>
+      <c r="G321" t="s">
+        <v>34</v>
+      </c>
+      <c r="H321" t="s">
+        <v>34</v>
+      </c>
+      <c r="I321" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A322" s="5">
+        <v>1020058</v>
+      </c>
+      <c r="B322" s="5">
+        <v>102</v>
+      </c>
+      <c r="C322" s="5">
+        <v>58</v>
+      </c>
+      <c r="D322" t="s">
+        <v>34</v>
+      </c>
+      <c r="E322" t="s">
+        <v>34</v>
+      </c>
+      <c r="F322" t="s">
+        <v>34</v>
+      </c>
+      <c r="G322" t="s">
+        <v>34</v>
+      </c>
+      <c r="H322" t="s">
+        <v>34</v>
+      </c>
+      <c r="I322" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A323" s="5">
+        <v>1020059</v>
+      </c>
+      <c r="B323" s="5">
+        <v>102</v>
+      </c>
+      <c r="C323" s="5">
+        <v>59</v>
+      </c>
+      <c r="D323" t="s">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>34</v>
+      </c>
+      <c r="G323" t="s">
+        <v>34</v>
+      </c>
+      <c r="H323" t="s">
+        <v>34</v>
+      </c>
+      <c r="I323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A324" s="5">
+        <v>1020060</v>
+      </c>
+      <c r="B324" s="5">
+        <v>102</v>
+      </c>
+      <c r="C324" s="5">
+        <v>60</v>
+      </c>
+      <c r="D324" t="s">
+        <v>34</v>
+      </c>
+      <c r="E324" t="s">
+        <v>34</v>
+      </c>
+      <c r="F324" t="s">
+        <v>34</v>
+      </c>
+      <c r="G324" t="s">
+        <v>34</v>
+      </c>
+      <c r="H324" t="s">
+        <v>34</v>
+      </c>
+      <c r="I324" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42672B62-EF56-4427-9D83-FBAD6DA40F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA1F00F-5532-49AE-91E8-BB5A5A8747D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="36">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,6 +163,10 @@
   </si>
   <si>
     <t>301:100_302:100_303:100_304:100_305:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>401:100_402:100_403:100_404:100_405:100_406:100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -539,7 +543,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I324"/>
+  <dimension ref="A1:I354"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" style="5" bestFit="1" customWidth="1"/>
@@ -9921,6 +9925,876 @@
         <v>34</v>
       </c>
     </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A325" s="5">
+        <v>1030001</v>
+      </c>
+      <c r="B325" s="5">
+        <v>103</v>
+      </c>
+      <c r="C325" s="5">
+        <v>1</v>
+      </c>
+      <c r="D325" t="s">
+        <v>35</v>
+      </c>
+      <c r="E325" t="s">
+        <v>35</v>
+      </c>
+      <c r="F325" t="s">
+        <v>35</v>
+      </c>
+      <c r="G325" t="s">
+        <v>35</v>
+      </c>
+      <c r="H325" t="s">
+        <v>35</v>
+      </c>
+      <c r="I325" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A326" s="5">
+        <v>1030002</v>
+      </c>
+      <c r="B326" s="5">
+        <v>103</v>
+      </c>
+      <c r="C326" s="5">
+        <v>2</v>
+      </c>
+      <c r="D326" t="s">
+        <v>35</v>
+      </c>
+      <c r="E326" t="s">
+        <v>35</v>
+      </c>
+      <c r="F326" t="s">
+        <v>35</v>
+      </c>
+      <c r="G326" t="s">
+        <v>35</v>
+      </c>
+      <c r="H326" t="s">
+        <v>35</v>
+      </c>
+      <c r="I326" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A327" s="5">
+        <v>1030003</v>
+      </c>
+      <c r="B327" s="5">
+        <v>103</v>
+      </c>
+      <c r="C327" s="5">
+        <v>3</v>
+      </c>
+      <c r="D327" t="s">
+        <v>35</v>
+      </c>
+      <c r="E327" t="s">
+        <v>35</v>
+      </c>
+      <c r="F327" t="s">
+        <v>35</v>
+      </c>
+      <c r="G327" t="s">
+        <v>35</v>
+      </c>
+      <c r="H327" t="s">
+        <v>35</v>
+      </c>
+      <c r="I327" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A328" s="5">
+        <v>1030004</v>
+      </c>
+      <c r="B328" s="5">
+        <v>103</v>
+      </c>
+      <c r="C328" s="5">
+        <v>4</v>
+      </c>
+      <c r="D328" t="s">
+        <v>35</v>
+      </c>
+      <c r="E328" t="s">
+        <v>35</v>
+      </c>
+      <c r="F328" t="s">
+        <v>35</v>
+      </c>
+      <c r="G328" t="s">
+        <v>35</v>
+      </c>
+      <c r="H328" t="s">
+        <v>35</v>
+      </c>
+      <c r="I328" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A329" s="5">
+        <v>1030005</v>
+      </c>
+      <c r="B329" s="5">
+        <v>103</v>
+      </c>
+      <c r="C329" s="5">
+        <v>5</v>
+      </c>
+      <c r="D329" t="s">
+        <v>35</v>
+      </c>
+      <c r="E329" t="s">
+        <v>35</v>
+      </c>
+      <c r="F329" t="s">
+        <v>35</v>
+      </c>
+      <c r="G329" t="s">
+        <v>35</v>
+      </c>
+      <c r="H329" t="s">
+        <v>35</v>
+      </c>
+      <c r="I329" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A330" s="5">
+        <v>1030006</v>
+      </c>
+      <c r="B330" s="5">
+        <v>103</v>
+      </c>
+      <c r="C330" s="5">
+        <v>6</v>
+      </c>
+      <c r="D330" t="s">
+        <v>35</v>
+      </c>
+      <c r="E330" t="s">
+        <v>35</v>
+      </c>
+      <c r="F330" t="s">
+        <v>35</v>
+      </c>
+      <c r="G330" t="s">
+        <v>35</v>
+      </c>
+      <c r="H330" t="s">
+        <v>35</v>
+      </c>
+      <c r="I330" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A331" s="5">
+        <v>1030007</v>
+      </c>
+      <c r="B331" s="5">
+        <v>103</v>
+      </c>
+      <c r="C331" s="5">
+        <v>7</v>
+      </c>
+      <c r="D331" t="s">
+        <v>35</v>
+      </c>
+      <c r="E331" t="s">
+        <v>35</v>
+      </c>
+      <c r="F331" t="s">
+        <v>35</v>
+      </c>
+      <c r="G331" t="s">
+        <v>35</v>
+      </c>
+      <c r="H331" t="s">
+        <v>35</v>
+      </c>
+      <c r="I331" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A332" s="5">
+        <v>1030008</v>
+      </c>
+      <c r="B332" s="5">
+        <v>103</v>
+      </c>
+      <c r="C332" s="5">
+        <v>8</v>
+      </c>
+      <c r="D332" t="s">
+        <v>35</v>
+      </c>
+      <c r="E332" t="s">
+        <v>35</v>
+      </c>
+      <c r="F332" t="s">
+        <v>35</v>
+      </c>
+      <c r="G332" t="s">
+        <v>35</v>
+      </c>
+      <c r="H332" t="s">
+        <v>35</v>
+      </c>
+      <c r="I332" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A333" s="5">
+        <v>1030009</v>
+      </c>
+      <c r="B333" s="5">
+        <v>103</v>
+      </c>
+      <c r="C333" s="5">
+        <v>9</v>
+      </c>
+      <c r="D333" t="s">
+        <v>35</v>
+      </c>
+      <c r="E333" t="s">
+        <v>35</v>
+      </c>
+      <c r="F333" t="s">
+        <v>35</v>
+      </c>
+      <c r="G333" t="s">
+        <v>35</v>
+      </c>
+      <c r="H333" t="s">
+        <v>35</v>
+      </c>
+      <c r="I333" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A334" s="5">
+        <v>1030010</v>
+      </c>
+      <c r="B334" s="5">
+        <v>103</v>
+      </c>
+      <c r="C334" s="5">
+        <v>10</v>
+      </c>
+      <c r="D334" t="s">
+        <v>35</v>
+      </c>
+      <c r="E334" t="s">
+        <v>35</v>
+      </c>
+      <c r="F334" t="s">
+        <v>35</v>
+      </c>
+      <c r="G334" t="s">
+        <v>35</v>
+      </c>
+      <c r="H334" t="s">
+        <v>35</v>
+      </c>
+      <c r="I334" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A335" s="5">
+        <v>1030011</v>
+      </c>
+      <c r="B335" s="5">
+        <v>103</v>
+      </c>
+      <c r="C335" s="5">
+        <v>11</v>
+      </c>
+      <c r="D335" t="s">
+        <v>35</v>
+      </c>
+      <c r="E335" t="s">
+        <v>35</v>
+      </c>
+      <c r="F335" t="s">
+        <v>35</v>
+      </c>
+      <c r="G335" t="s">
+        <v>35</v>
+      </c>
+      <c r="H335" t="s">
+        <v>35</v>
+      </c>
+      <c r="I335" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A336" s="5">
+        <v>1030012</v>
+      </c>
+      <c r="B336" s="5">
+        <v>103</v>
+      </c>
+      <c r="C336" s="5">
+        <v>12</v>
+      </c>
+      <c r="D336" t="s">
+        <v>35</v>
+      </c>
+      <c r="E336" t="s">
+        <v>35</v>
+      </c>
+      <c r="F336" t="s">
+        <v>35</v>
+      </c>
+      <c r="G336" t="s">
+        <v>35</v>
+      </c>
+      <c r="H336" t="s">
+        <v>35</v>
+      </c>
+      <c r="I336" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A337" s="5">
+        <v>1030013</v>
+      </c>
+      <c r="B337" s="5">
+        <v>103</v>
+      </c>
+      <c r="C337" s="5">
+        <v>13</v>
+      </c>
+      <c r="D337" t="s">
+        <v>35</v>
+      </c>
+      <c r="E337" t="s">
+        <v>35</v>
+      </c>
+      <c r="F337" t="s">
+        <v>35</v>
+      </c>
+      <c r="G337" t="s">
+        <v>35</v>
+      </c>
+      <c r="H337" t="s">
+        <v>35</v>
+      </c>
+      <c r="I337" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A338" s="5">
+        <v>1030014</v>
+      </c>
+      <c r="B338" s="5">
+        <v>103</v>
+      </c>
+      <c r="C338" s="5">
+        <v>14</v>
+      </c>
+      <c r="D338" t="s">
+        <v>35</v>
+      </c>
+      <c r="E338" t="s">
+        <v>35</v>
+      </c>
+      <c r="F338" t="s">
+        <v>35</v>
+      </c>
+      <c r="G338" t="s">
+        <v>35</v>
+      </c>
+      <c r="H338" t="s">
+        <v>35</v>
+      </c>
+      <c r="I338" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A339" s="5">
+        <v>1030015</v>
+      </c>
+      <c r="B339" s="5">
+        <v>103</v>
+      </c>
+      <c r="C339" s="5">
+        <v>15</v>
+      </c>
+      <c r="D339" t="s">
+        <v>35</v>
+      </c>
+      <c r="E339" t="s">
+        <v>35</v>
+      </c>
+      <c r="F339" t="s">
+        <v>35</v>
+      </c>
+      <c r="G339" t="s">
+        <v>35</v>
+      </c>
+      <c r="H339" t="s">
+        <v>35</v>
+      </c>
+      <c r="I339" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A340" s="5">
+        <v>1030016</v>
+      </c>
+      <c r="B340" s="5">
+        <v>103</v>
+      </c>
+      <c r="C340" s="5">
+        <v>16</v>
+      </c>
+      <c r="D340" t="s">
+        <v>35</v>
+      </c>
+      <c r="E340" t="s">
+        <v>35</v>
+      </c>
+      <c r="F340" t="s">
+        <v>35</v>
+      </c>
+      <c r="G340" t="s">
+        <v>35</v>
+      </c>
+      <c r="H340" t="s">
+        <v>35</v>
+      </c>
+      <c r="I340" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A341" s="5">
+        <v>1030017</v>
+      </c>
+      <c r="B341" s="5">
+        <v>103</v>
+      </c>
+      <c r="C341" s="5">
+        <v>17</v>
+      </c>
+      <c r="D341" t="s">
+        <v>35</v>
+      </c>
+      <c r="E341" t="s">
+        <v>35</v>
+      </c>
+      <c r="F341" t="s">
+        <v>35</v>
+      </c>
+      <c r="G341" t="s">
+        <v>35</v>
+      </c>
+      <c r="H341" t="s">
+        <v>35</v>
+      </c>
+      <c r="I341" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A342" s="5">
+        <v>1030018</v>
+      </c>
+      <c r="B342" s="5">
+        <v>103</v>
+      </c>
+      <c r="C342" s="5">
+        <v>18</v>
+      </c>
+      <c r="D342" t="s">
+        <v>35</v>
+      </c>
+      <c r="E342" t="s">
+        <v>35</v>
+      </c>
+      <c r="F342" t="s">
+        <v>35</v>
+      </c>
+      <c r="G342" t="s">
+        <v>35</v>
+      </c>
+      <c r="H342" t="s">
+        <v>35</v>
+      </c>
+      <c r="I342" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A343" s="5">
+        <v>1030019</v>
+      </c>
+      <c r="B343" s="5">
+        <v>103</v>
+      </c>
+      <c r="C343" s="5">
+        <v>19</v>
+      </c>
+      <c r="D343" t="s">
+        <v>35</v>
+      </c>
+      <c r="E343" t="s">
+        <v>35</v>
+      </c>
+      <c r="F343" t="s">
+        <v>35</v>
+      </c>
+      <c r="G343" t="s">
+        <v>35</v>
+      </c>
+      <c r="H343" t="s">
+        <v>35</v>
+      </c>
+      <c r="I343" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A344" s="5">
+        <v>1030020</v>
+      </c>
+      <c r="B344" s="5">
+        <v>103</v>
+      </c>
+      <c r="C344" s="5">
+        <v>20</v>
+      </c>
+      <c r="D344" t="s">
+        <v>35</v>
+      </c>
+      <c r="E344" t="s">
+        <v>35</v>
+      </c>
+      <c r="F344" t="s">
+        <v>35</v>
+      </c>
+      <c r="G344" t="s">
+        <v>35</v>
+      </c>
+      <c r="H344" t="s">
+        <v>35</v>
+      </c>
+      <c r="I344" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A345" s="5">
+        <v>1030021</v>
+      </c>
+      <c r="B345" s="5">
+        <v>103</v>
+      </c>
+      <c r="C345" s="5">
+        <v>21</v>
+      </c>
+      <c r="D345" t="s">
+        <v>35</v>
+      </c>
+      <c r="E345" t="s">
+        <v>35</v>
+      </c>
+      <c r="F345" t="s">
+        <v>35</v>
+      </c>
+      <c r="G345" t="s">
+        <v>35</v>
+      </c>
+      <c r="H345" t="s">
+        <v>35</v>
+      </c>
+      <c r="I345" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A346" s="5">
+        <v>1030022</v>
+      </c>
+      <c r="B346" s="5">
+        <v>103</v>
+      </c>
+      <c r="C346" s="5">
+        <v>22</v>
+      </c>
+      <c r="D346" t="s">
+        <v>35</v>
+      </c>
+      <c r="E346" t="s">
+        <v>35</v>
+      </c>
+      <c r="F346" t="s">
+        <v>35</v>
+      </c>
+      <c r="G346" t="s">
+        <v>35</v>
+      </c>
+      <c r="H346" t="s">
+        <v>35</v>
+      </c>
+      <c r="I346" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A347" s="5">
+        <v>1030023</v>
+      </c>
+      <c r="B347" s="5">
+        <v>103</v>
+      </c>
+      <c r="C347" s="5">
+        <v>23</v>
+      </c>
+      <c r="D347" t="s">
+        <v>35</v>
+      </c>
+      <c r="E347" t="s">
+        <v>35</v>
+      </c>
+      <c r="F347" t="s">
+        <v>35</v>
+      </c>
+      <c r="G347" t="s">
+        <v>35</v>
+      </c>
+      <c r="H347" t="s">
+        <v>35</v>
+      </c>
+      <c r="I347" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A348" s="5">
+        <v>1030024</v>
+      </c>
+      <c r="B348" s="5">
+        <v>103</v>
+      </c>
+      <c r="C348" s="5">
+        <v>24</v>
+      </c>
+      <c r="D348" t="s">
+        <v>35</v>
+      </c>
+      <c r="E348" t="s">
+        <v>35</v>
+      </c>
+      <c r="F348" t="s">
+        <v>35</v>
+      </c>
+      <c r="G348" t="s">
+        <v>35</v>
+      </c>
+      <c r="H348" t="s">
+        <v>35</v>
+      </c>
+      <c r="I348" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A349" s="5">
+        <v>1030025</v>
+      </c>
+      <c r="B349" s="5">
+        <v>103</v>
+      </c>
+      <c r="C349" s="5">
+        <v>25</v>
+      </c>
+      <c r="D349" t="s">
+        <v>35</v>
+      </c>
+      <c r="E349" t="s">
+        <v>35</v>
+      </c>
+      <c r="F349" t="s">
+        <v>35</v>
+      </c>
+      <c r="G349" t="s">
+        <v>35</v>
+      </c>
+      <c r="H349" t="s">
+        <v>35</v>
+      </c>
+      <c r="I349" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A350" s="5">
+        <v>1030026</v>
+      </c>
+      <c r="B350" s="5">
+        <v>103</v>
+      </c>
+      <c r="C350" s="5">
+        <v>26</v>
+      </c>
+      <c r="D350" t="s">
+        <v>35</v>
+      </c>
+      <c r="E350" t="s">
+        <v>35</v>
+      </c>
+      <c r="F350" t="s">
+        <v>35</v>
+      </c>
+      <c r="G350" t="s">
+        <v>35</v>
+      </c>
+      <c r="H350" t="s">
+        <v>35</v>
+      </c>
+      <c r="I350" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A351" s="5">
+        <v>1030027</v>
+      </c>
+      <c r="B351" s="5">
+        <v>103</v>
+      </c>
+      <c r="C351" s="5">
+        <v>27</v>
+      </c>
+      <c r="D351" t="s">
+        <v>35</v>
+      </c>
+      <c r="E351" t="s">
+        <v>35</v>
+      </c>
+      <c r="F351" t="s">
+        <v>35</v>
+      </c>
+      <c r="G351" t="s">
+        <v>35</v>
+      </c>
+      <c r="H351" t="s">
+        <v>35</v>
+      </c>
+      <c r="I351" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A352" s="5">
+        <v>1030028</v>
+      </c>
+      <c r="B352" s="5">
+        <v>103</v>
+      </c>
+      <c r="C352" s="5">
+        <v>28</v>
+      </c>
+      <c r="D352" t="s">
+        <v>35</v>
+      </c>
+      <c r="E352" t="s">
+        <v>35</v>
+      </c>
+      <c r="F352" t="s">
+        <v>35</v>
+      </c>
+      <c r="G352" t="s">
+        <v>35</v>
+      </c>
+      <c r="H352" t="s">
+        <v>35</v>
+      </c>
+      <c r="I352" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A353" s="5">
+        <v>1030029</v>
+      </c>
+      <c r="B353" s="5">
+        <v>103</v>
+      </c>
+      <c r="C353" s="5">
+        <v>29</v>
+      </c>
+      <c r="D353" t="s">
+        <v>35</v>
+      </c>
+      <c r="E353" t="s">
+        <v>35</v>
+      </c>
+      <c r="F353" t="s">
+        <v>35</v>
+      </c>
+      <c r="G353" t="s">
+        <v>35</v>
+      </c>
+      <c r="H353" t="s">
+        <v>35</v>
+      </c>
+      <c r="I353" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A354" s="5">
+        <v>1030030</v>
+      </c>
+      <c r="B354" s="5">
+        <v>103</v>
+      </c>
+      <c r="C354" s="5">
+        <v>30</v>
+      </c>
+      <c r="D354" t="s">
+        <v>35</v>
+      </c>
+      <c r="E354" t="s">
+        <v>35</v>
+      </c>
+      <c r="F354" t="s">
+        <v>35</v>
+      </c>
+      <c r="G354" t="s">
+        <v>35</v>
+      </c>
+      <c r="H354" t="s">
+        <v>35</v>
+      </c>
+      <c r="I354" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA1F00F-5532-49AE-91E8-BB5A5A8747D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3FE12A-DB6B-4E88-BDA6-A413D9A308FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_rand_rule_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="38">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -166,7 +166,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>401:100_402:100_403:100_404:100_405:100_406:100</t>
+    <t>401:100_402:100_403:100_404:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>405:100_406:100_407:100_408:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9939,19 +9947,19 @@
         <v>35</v>
       </c>
       <c r="E325" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F325" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G325" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H325" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I325" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.2">
@@ -9968,19 +9976,19 @@
         <v>35</v>
       </c>
       <c r="E326" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F326" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G326" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H326" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I326" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.2">
@@ -9997,19 +10005,19 @@
         <v>35</v>
       </c>
       <c r="E327" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F327" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G327" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H327" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I327" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.2">
@@ -10026,19 +10034,19 @@
         <v>35</v>
       </c>
       <c r="E328" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F328" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G328" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H328" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I328" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.2">
@@ -10055,19 +10063,19 @@
         <v>35</v>
       </c>
       <c r="E329" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F329" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G329" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H329" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I329" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.2">
@@ -10084,19 +10092,19 @@
         <v>35</v>
       </c>
       <c r="E330" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F330" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G330" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H330" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I330" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.2">
@@ -10113,19 +10121,19 @@
         <v>35</v>
       </c>
       <c r="E331" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F331" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G331" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H331" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I331" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.2">
@@ -10142,19 +10150,19 @@
         <v>35</v>
       </c>
       <c r="E332" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F332" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G332" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H332" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I332" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.2">
@@ -10171,19 +10179,19 @@
         <v>35</v>
       </c>
       <c r="E333" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F333" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G333" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H333" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I333" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.2">
@@ -10200,19 +10208,19 @@
         <v>35</v>
       </c>
       <c r="E334" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F334" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G334" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H334" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I334" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.2">
@@ -10229,19 +10237,19 @@
         <v>35</v>
       </c>
       <c r="E335" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F335" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G335" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H335" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I335" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.2">
@@ -10258,19 +10266,19 @@
         <v>35</v>
       </c>
       <c r="E336" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F336" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G336" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H336" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I336" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.2">
@@ -10287,19 +10295,19 @@
         <v>35</v>
       </c>
       <c r="E337" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F337" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G337" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H337" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I337" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.2">
@@ -10316,19 +10324,19 @@
         <v>35</v>
       </c>
       <c r="E338" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F338" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G338" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H338" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I338" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.2">
@@ -10345,19 +10353,19 @@
         <v>35</v>
       </c>
       <c r="E339" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F339" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G339" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H339" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I339" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.2">
@@ -10374,19 +10382,19 @@
         <v>35</v>
       </c>
       <c r="E340" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F340" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G340" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H340" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I340" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.2">
@@ -10403,19 +10411,19 @@
         <v>35</v>
       </c>
       <c r="E341" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F341" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G341" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H341" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I341" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.2">
@@ -10432,19 +10440,19 @@
         <v>35</v>
       </c>
       <c r="E342" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F342" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G342" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H342" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I342" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.2">
@@ -10461,19 +10469,19 @@
         <v>35</v>
       </c>
       <c r="E343" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F343" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G343" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H343" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I343" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.2">
@@ -10490,19 +10498,19 @@
         <v>35</v>
       </c>
       <c r="E344" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F344" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G344" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H344" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I344" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.2">
@@ -10519,19 +10527,19 @@
         <v>35</v>
       </c>
       <c r="E345" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F345" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G345" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H345" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I345" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.2">
@@ -10548,19 +10556,19 @@
         <v>35</v>
       </c>
       <c r="E346" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F346" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G346" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H346" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I346" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.2">
@@ -10577,19 +10585,19 @@
         <v>35</v>
       </c>
       <c r="E347" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F347" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G347" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H347" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I347" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.2">
@@ -10606,19 +10614,19 @@
         <v>35</v>
       </c>
       <c r="E348" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F348" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G348" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H348" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I348" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.2">
@@ -10635,19 +10643,19 @@
         <v>35</v>
       </c>
       <c r="E349" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F349" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G349" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H349" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I349" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.2">
@@ -10664,19 +10672,19 @@
         <v>35</v>
       </c>
       <c r="E350" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F350" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G350" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H350" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I350" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.2">
@@ -10693,19 +10701,19 @@
         <v>35</v>
       </c>
       <c r="E351" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F351" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G351" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H351" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I351" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.2">
@@ -10722,19 +10730,19 @@
         <v>35</v>
       </c>
       <c r="E352" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F352" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G352" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H352" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I352" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.2">
@@ -10751,19 +10759,19 @@
         <v>35</v>
       </c>
       <c r="E353" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F353" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G353" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H353" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I353" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.2">
@@ -10780,19 +10788,19 @@
         <v>35</v>
       </c>
       <c r="E354" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F354" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G354" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H354" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I354" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3FE12A-DB6B-4E88-BDA6-A413D9A308FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580881D0-BCAB-4E1E-9B96-9AC31CAE6411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="39">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -175,6 +175,10 @@
   </si>
   <si>
     <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100_409:200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10008,7 +10012,7 @@
         <v>36</v>
       </c>
       <c r="F327" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G327" t="s">
         <v>37</v>
@@ -10037,7 +10041,7 @@
         <v>36</v>
       </c>
       <c r="F328" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G328" t="s">
         <v>37</v>
@@ -10066,7 +10070,7 @@
         <v>36</v>
       </c>
       <c r="F329" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G329" t="s">
         <v>37</v>
@@ -10095,7 +10099,7 @@
         <v>36</v>
       </c>
       <c r="F330" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G330" t="s">
         <v>37</v>
@@ -10124,7 +10128,7 @@
         <v>36</v>
       </c>
       <c r="F331" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G331" t="s">
         <v>37</v>
@@ -10153,7 +10157,7 @@
         <v>36</v>
       </c>
       <c r="F332" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G332" t="s">
         <v>37</v>
@@ -10182,7 +10186,7 @@
         <v>36</v>
       </c>
       <c r="F333" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G333" t="s">
         <v>37</v>
@@ -10211,7 +10215,7 @@
         <v>36</v>
       </c>
       <c r="F334" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G334" t="s">
         <v>37</v>
@@ -10240,7 +10244,7 @@
         <v>36</v>
       </c>
       <c r="F335" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G335" t="s">
         <v>37</v>
@@ -10269,7 +10273,7 @@
         <v>36</v>
       </c>
       <c r="F336" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G336" t="s">
         <v>37</v>
@@ -10298,7 +10302,7 @@
         <v>36</v>
       </c>
       <c r="F337" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G337" t="s">
         <v>37</v>
@@ -10327,7 +10331,7 @@
         <v>36</v>
       </c>
       <c r="F338" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G338" t="s">
         <v>37</v>
@@ -10356,7 +10360,7 @@
         <v>36</v>
       </c>
       <c r="F339" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G339" t="s">
         <v>37</v>
@@ -10385,7 +10389,7 @@
         <v>36</v>
       </c>
       <c r="F340" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G340" t="s">
         <v>37</v>
@@ -10414,7 +10418,7 @@
         <v>36</v>
       </c>
       <c r="F341" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G341" t="s">
         <v>37</v>
@@ -10443,7 +10447,7 @@
         <v>36</v>
       </c>
       <c r="F342" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G342" t="s">
         <v>37</v>
@@ -10472,7 +10476,7 @@
         <v>36</v>
       </c>
       <c r="F343" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G343" t="s">
         <v>37</v>
@@ -10501,7 +10505,7 @@
         <v>36</v>
       </c>
       <c r="F344" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G344" t="s">
         <v>37</v>
@@ -10530,7 +10534,7 @@
         <v>36</v>
       </c>
       <c r="F345" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G345" t="s">
         <v>37</v>
@@ -10559,7 +10563,7 @@
         <v>36</v>
       </c>
       <c r="F346" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G346" t="s">
         <v>37</v>
@@ -10588,7 +10592,7 @@
         <v>36</v>
       </c>
       <c r="F347" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G347" t="s">
         <v>37</v>
@@ -10617,7 +10621,7 @@
         <v>36</v>
       </c>
       <c r="F348" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G348" t="s">
         <v>37</v>
@@ -10646,7 +10650,7 @@
         <v>36</v>
       </c>
       <c r="F349" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G349" t="s">
         <v>37</v>
@@ -10675,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="F350" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G350" t="s">
         <v>37</v>
@@ -10704,7 +10708,7 @@
         <v>36</v>
       </c>
       <c r="F351" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G351" t="s">
         <v>37</v>
@@ -10733,7 +10737,7 @@
         <v>36</v>
       </c>
       <c r="F352" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G352" t="s">
         <v>37</v>
@@ -10762,7 +10766,7 @@
         <v>36</v>
       </c>
       <c r="F353" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G353" t="s">
         <v>37</v>
@@ -10791,7 +10795,7 @@
         <v>36</v>
       </c>
       <c r="F354" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G354" t="s">
         <v>37</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580881D0-BCAB-4E1E-9B96-9AC31CAE6411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627048C1-C55C-4F6D-A584-B237008E5658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="38">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -166,19 +166,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>401:100_402:100_403:100_404:100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>405:100_406:100_407:100_408:100</t>
+    <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100_409:200</t>
+    <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100_409:400</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9951,19 +9946,19 @@
         <v>35</v>
       </c>
       <c r="E325" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F325" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G325" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H325" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I325" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.2">
@@ -9980,19 +9975,19 @@
         <v>35</v>
       </c>
       <c r="E326" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F326" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G326" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H326" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I326" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.2">
@@ -10006,22 +10001,22 @@
         <v>3</v>
       </c>
       <c r="D327" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E327" t="s">
         <v>36</v>
       </c>
       <c r="F327" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G327" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H327" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I327" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.2">
@@ -10035,22 +10030,22 @@
         <v>4</v>
       </c>
       <c r="D328" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E328" t="s">
         <v>36</v>
       </c>
       <c r="F328" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G328" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H328" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I328" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.2">
@@ -10064,22 +10059,22 @@
         <v>5</v>
       </c>
       <c r="D329" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E329" t="s">
         <v>36</v>
       </c>
       <c r="F329" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G329" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H329" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I329" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.2">
@@ -10093,22 +10088,22 @@
         <v>6</v>
       </c>
       <c r="D330" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E330" t="s">
         <v>36</v>
       </c>
       <c r="F330" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G330" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H330" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I330" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.2">
@@ -10122,22 +10117,22 @@
         <v>7</v>
       </c>
       <c r="D331" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E331" t="s">
         <v>36</v>
       </c>
       <c r="F331" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G331" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H331" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I331" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.2">
@@ -10151,22 +10146,22 @@
         <v>8</v>
       </c>
       <c r="D332" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E332" t="s">
         <v>36</v>
       </c>
       <c r="F332" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G332" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H332" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I332" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.2">
@@ -10180,22 +10175,22 @@
         <v>9</v>
       </c>
       <c r="D333" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E333" t="s">
         <v>36</v>
       </c>
       <c r="F333" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G333" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H333" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I333" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.2">
@@ -10209,22 +10204,22 @@
         <v>10</v>
       </c>
       <c r="D334" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E334" t="s">
         <v>36</v>
       </c>
       <c r="F334" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G334" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H334" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I334" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.2">
@@ -10238,22 +10233,22 @@
         <v>11</v>
       </c>
       <c r="D335" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E335" t="s">
         <v>36</v>
       </c>
       <c r="F335" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G335" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H335" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I335" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.2">
@@ -10267,22 +10262,22 @@
         <v>12</v>
       </c>
       <c r="D336" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E336" t="s">
         <v>36</v>
       </c>
       <c r="F336" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G336" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H336" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I336" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.2">
@@ -10296,22 +10291,22 @@
         <v>13</v>
       </c>
       <c r="D337" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E337" t="s">
         <v>36</v>
       </c>
       <c r="F337" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G337" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H337" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I337" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.2">
@@ -10325,22 +10320,22 @@
         <v>14</v>
       </c>
       <c r="D338" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E338" t="s">
         <v>36</v>
       </c>
       <c r="F338" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G338" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H338" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I338" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.2">
@@ -10354,22 +10349,22 @@
         <v>15</v>
       </c>
       <c r="D339" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E339" t="s">
         <v>36</v>
       </c>
       <c r="F339" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G339" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H339" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I339" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.2">
@@ -10383,22 +10378,22 @@
         <v>16</v>
       </c>
       <c r="D340" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E340" t="s">
         <v>36</v>
       </c>
       <c r="F340" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G340" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H340" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I340" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.2">
@@ -10412,22 +10407,22 @@
         <v>17</v>
       </c>
       <c r="D341" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E341" t="s">
         <v>36</v>
       </c>
       <c r="F341" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G341" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H341" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I341" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.2">
@@ -10441,22 +10436,22 @@
         <v>18</v>
       </c>
       <c r="D342" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E342" t="s">
         <v>36</v>
       </c>
       <c r="F342" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G342" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H342" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I342" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.2">
@@ -10470,22 +10465,22 @@
         <v>19</v>
       </c>
       <c r="D343" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E343" t="s">
         <v>36</v>
       </c>
       <c r="F343" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G343" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H343" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I343" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.2">
@@ -10499,22 +10494,22 @@
         <v>20</v>
       </c>
       <c r="D344" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E344" t="s">
         <v>36</v>
       </c>
       <c r="F344" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G344" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H344" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I344" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.2">
@@ -10528,22 +10523,22 @@
         <v>21</v>
       </c>
       <c r="D345" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E345" t="s">
         <v>36</v>
       </c>
       <c r="F345" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G345" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H345" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I345" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.2">
@@ -10557,22 +10552,22 @@
         <v>22</v>
       </c>
       <c r="D346" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E346" t="s">
         <v>36</v>
       </c>
       <c r="F346" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G346" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H346" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I346" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.2">
@@ -10586,22 +10581,22 @@
         <v>23</v>
       </c>
       <c r="D347" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E347" t="s">
         <v>36</v>
       </c>
       <c r="F347" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G347" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H347" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I347" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.2">
@@ -10615,22 +10610,22 @@
         <v>24</v>
       </c>
       <c r="D348" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E348" t="s">
         <v>36</v>
       </c>
       <c r="F348" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G348" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H348" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I348" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.2">
@@ -10644,22 +10639,22 @@
         <v>25</v>
       </c>
       <c r="D349" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E349" t="s">
         <v>36</v>
       </c>
       <c r="F349" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G349" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H349" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I349" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.2">
@@ -10673,22 +10668,22 @@
         <v>26</v>
       </c>
       <c r="D350" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E350" t="s">
         <v>36</v>
       </c>
       <c r="F350" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G350" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H350" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I350" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.2">
@@ -10702,22 +10697,22 @@
         <v>27</v>
       </c>
       <c r="D351" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E351" t="s">
         <v>36</v>
       </c>
       <c r="F351" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G351" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H351" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I351" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.2">
@@ -10731,22 +10726,22 @@
         <v>28</v>
       </c>
       <c r="D352" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E352" t="s">
         <v>36</v>
       </c>
       <c r="F352" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G352" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H352" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I352" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.2">
@@ -10760,22 +10755,22 @@
         <v>29</v>
       </c>
       <c r="D353" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E353" t="s">
         <v>36</v>
       </c>
       <c r="F353" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G353" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H353" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I353" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.2">
@@ -10789,22 +10784,22 @@
         <v>30</v>
       </c>
       <c r="D354" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E354" t="s">
         <v>36</v>
       </c>
       <c r="F354" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G354" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H354" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I354" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627048C1-C55C-4F6D-A584-B237008E5658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10FB981-F7C4-40BC-BEAC-BA6EBC818C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_rand_rule_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="37">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -156,10 +156,6 @@
   </si>
   <si>
     <t>201:100_202:100_203:100_204:100_205:100</t>
-  </si>
-  <si>
-    <t>201:100_202:100_203:100_204:100_205:100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>301:100_302:100_303:100_304:100_305:100</t>
@@ -550,7 +546,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I354"/>
+  <dimension ref="A1:I345"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" style="5" bestFit="1" customWidth="1"/>
@@ -654,13 +650,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
-        <v>100000001</v>
+        <v>100000002</v>
       </c>
       <c r="B5" s="5">
         <v>10000</v>
       </c>
       <c r="C5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -683,13 +679,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
-        <v>100000002</v>
+        <v>100000003</v>
       </c>
       <c r="B6" s="5">
         <v>10000</v>
       </c>
       <c r="C6" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
@@ -712,13 +708,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
-        <v>100000003</v>
+        <v>100000004</v>
       </c>
       <c r="B7" s="5">
         <v>10000</v>
       </c>
       <c r="C7" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
@@ -741,13 +737,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
-        <v>100000004</v>
+        <v>100000005</v>
       </c>
       <c r="B8" s="5">
         <v>10000</v>
       </c>
       <c r="C8" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -770,13 +766,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
-        <v>100000005</v>
+        <v>100000006</v>
       </c>
       <c r="B9" s="5">
         <v>10000</v>
       </c>
       <c r="C9" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -799,13 +795,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
-        <v>100000006</v>
+        <v>100000007</v>
       </c>
       <c r="B10" s="5">
         <v>10000</v>
       </c>
       <c r="C10" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
@@ -828,13 +824,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
-        <v>100000007</v>
+        <v>100000008</v>
       </c>
       <c r="B11" s="5">
         <v>10000</v>
       </c>
       <c r="C11" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
@@ -857,13 +853,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
-        <v>100000008</v>
+        <v>100000009</v>
       </c>
       <c r="B12" s="5">
         <v>10000</v>
       </c>
       <c r="C12" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -886,13 +882,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
-        <v>100000009</v>
+        <v>100000010</v>
       </c>
       <c r="B13" s="5">
         <v>10000</v>
       </c>
       <c r="C13" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -915,13 +911,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
-        <v>100000010</v>
+        <v>100000011</v>
       </c>
       <c r="B14" s="5">
         <v>10000</v>
       </c>
       <c r="C14" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
@@ -944,13 +940,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
-        <v>100000011</v>
+        <v>100000012</v>
       </c>
       <c r="B15" s="5">
         <v>10000</v>
       </c>
       <c r="C15" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
         <v>16</v>
@@ -973,13 +969,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
-        <v>100000012</v>
+        <v>100000013</v>
       </c>
       <c r="B16" s="5">
         <v>10000</v>
       </c>
       <c r="C16" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
         <v>16</v>
@@ -1002,13 +998,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
-        <v>100000013</v>
+        <v>100000014</v>
       </c>
       <c r="B17" s="5">
         <v>10000</v>
       </c>
       <c r="C17" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
         <v>16</v>
@@ -1031,13 +1027,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
-        <v>100000014</v>
+        <v>100000015</v>
       </c>
       <c r="B18" s="5">
         <v>10000</v>
       </c>
       <c r="C18" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
@@ -1060,13 +1056,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
-        <v>100000015</v>
+        <v>100000016</v>
       </c>
       <c r="B19" s="5">
         <v>10000</v>
       </c>
       <c r="C19" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
         <v>16</v>
@@ -1089,13 +1085,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
-        <v>100000016</v>
+        <v>100000017</v>
       </c>
       <c r="B20" s="5">
         <v>10000</v>
       </c>
       <c r="C20" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
         <v>16</v>
@@ -1118,13 +1114,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
-        <v>100000017</v>
+        <v>100000018</v>
       </c>
       <c r="B21" s="5">
         <v>10000</v>
       </c>
       <c r="C21" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
         <v>16</v>
@@ -1147,13 +1143,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
-        <v>100000018</v>
+        <v>100000019</v>
       </c>
       <c r="B22" s="5">
         <v>10000</v>
       </c>
       <c r="C22" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
         <v>16</v>
@@ -1176,13 +1172,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
-        <v>100000019</v>
+        <v>100000020</v>
       </c>
       <c r="B23" s="5">
         <v>10000</v>
       </c>
       <c r="C23" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
         <v>16</v>
@@ -1205,13 +1201,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
-        <v>100000020</v>
+        <v>100000021</v>
       </c>
       <c r="B24" s="5">
         <v>10000</v>
       </c>
       <c r="C24" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
         <v>16</v>
@@ -1234,13 +1230,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
-        <v>100000021</v>
+        <v>100000022</v>
       </c>
       <c r="B25" s="5">
         <v>10000</v>
       </c>
       <c r="C25" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D25" t="s">
         <v>16</v>
@@ -1263,13 +1259,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
-        <v>100000022</v>
+        <v>100000023</v>
       </c>
       <c r="B26" s="5">
         <v>10000</v>
       </c>
       <c r="C26" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
@@ -1292,13 +1288,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
-        <v>100000023</v>
+        <v>100000024</v>
       </c>
       <c r="B27" s="5">
         <v>10000</v>
       </c>
       <c r="C27" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
         <v>16</v>
@@ -1321,13 +1317,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
-        <v>100000024</v>
+        <v>100000025</v>
       </c>
       <c r="B28" s="5">
         <v>10000</v>
       </c>
       <c r="C28" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
         <v>16</v>
@@ -1350,13 +1346,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
-        <v>100000025</v>
+        <v>100000026</v>
       </c>
       <c r="B29" s="5">
         <v>10000</v>
       </c>
       <c r="C29" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
@@ -1379,13 +1375,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
-        <v>100000026</v>
+        <v>100000027</v>
       </c>
       <c r="B30" s="5">
         <v>10000</v>
       </c>
       <c r="C30" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
         <v>16</v>
@@ -1408,13 +1404,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
-        <v>100000027</v>
+        <v>100000028</v>
       </c>
       <c r="B31" s="5">
         <v>10000</v>
       </c>
       <c r="C31" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
         <v>16</v>
@@ -1437,13 +1433,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
-        <v>100000028</v>
+        <v>100000029</v>
       </c>
       <c r="B32" s="5">
         <v>10000</v>
       </c>
       <c r="C32" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
         <v>16</v>
@@ -1466,13 +1462,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
-        <v>100000029</v>
+        <v>100000030</v>
       </c>
       <c r="B33" s="5">
         <v>10000</v>
       </c>
       <c r="C33" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D33" t="s">
         <v>16</v>
@@ -1495,42 +1491,42 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
-        <v>100000030</v>
+        <v>10002</v>
       </c>
       <c r="B34" s="5">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="C34" s="5">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I34" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
-        <v>10001</v>
+        <v>10003</v>
       </c>
       <c r="B35" s="5">
         <v>1</v>
       </c>
       <c r="C35" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -1553,13 +1549,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
-        <v>10002</v>
+        <v>10004</v>
       </c>
       <c r="B36" s="5">
         <v>1</v>
       </c>
       <c r="C36" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -1582,13 +1578,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
-        <v>10003</v>
+        <v>10005</v>
       </c>
       <c r="B37" s="5">
         <v>1</v>
       </c>
       <c r="C37" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -1611,13 +1607,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
-        <v>10004</v>
+        <v>10006</v>
       </c>
       <c r="B38" s="5">
         <v>1</v>
       </c>
       <c r="C38" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -1640,13 +1636,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
-        <v>10005</v>
+        <v>10007</v>
       </c>
       <c r="B39" s="5">
         <v>1</v>
       </c>
       <c r="C39" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -1669,13 +1665,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
-        <v>10006</v>
+        <v>10008</v>
       </c>
       <c r="B40" s="5">
         <v>1</v>
       </c>
       <c r="C40" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -1698,13 +1694,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
-        <v>10007</v>
+        <v>10009</v>
       </c>
       <c r="B41" s="5">
         <v>1</v>
       </c>
       <c r="C41" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -1727,13 +1723,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
-        <v>10008</v>
+        <v>10010</v>
       </c>
       <c r="B42" s="5">
         <v>1</v>
       </c>
       <c r="C42" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -1756,13 +1752,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
-        <v>10009</v>
+        <v>10011</v>
       </c>
       <c r="B43" s="5">
         <v>1</v>
       </c>
       <c r="C43" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -1785,13 +1781,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
-        <v>10010</v>
+        <v>10012</v>
       </c>
       <c r="B44" s="5">
         <v>1</v>
       </c>
       <c r="C44" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -1814,13 +1810,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
-        <v>10011</v>
+        <v>10013</v>
       </c>
       <c r="B45" s="5">
         <v>1</v>
       </c>
       <c r="C45" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -1843,13 +1839,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
-        <v>10012</v>
+        <v>10014</v>
       </c>
       <c r="B46" s="5">
         <v>1</v>
       </c>
       <c r="C46" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -1872,13 +1868,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
-        <v>10013</v>
+        <v>10015</v>
       </c>
       <c r="B47" s="5">
         <v>1</v>
       </c>
       <c r="C47" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -1901,13 +1897,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
-        <v>10014</v>
+        <v>10016</v>
       </c>
       <c r="B48" s="5">
         <v>1</v>
       </c>
       <c r="C48" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -1930,13 +1926,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
-        <v>10015</v>
+        <v>10017</v>
       </c>
       <c r="B49" s="5">
         <v>1</v>
       </c>
       <c r="C49" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -1959,13 +1955,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
-        <v>10016</v>
+        <v>10018</v>
       </c>
       <c r="B50" s="5">
         <v>1</v>
       </c>
       <c r="C50" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -1988,13 +1984,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
-        <v>10017</v>
+        <v>10019</v>
       </c>
       <c r="B51" s="5">
         <v>1</v>
       </c>
       <c r="C51" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -2017,13 +2013,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
-        <v>10018</v>
+        <v>10020</v>
       </c>
       <c r="B52" s="5">
         <v>1</v>
       </c>
       <c r="C52" s="5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -2046,13 +2042,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
-        <v>10019</v>
+        <v>10021</v>
       </c>
       <c r="B53" s="5">
         <v>1</v>
       </c>
       <c r="C53" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -2075,13 +2071,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
-        <v>10020</v>
+        <v>10022</v>
       </c>
       <c r="B54" s="5">
         <v>1</v>
       </c>
       <c r="C54" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D54" t="s">
         <v>17</v>
@@ -2104,13 +2100,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
-        <v>10021</v>
+        <v>10023</v>
       </c>
       <c r="B55" s="5">
         <v>1</v>
       </c>
       <c r="C55" s="5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D55" t="s">
         <v>17</v>
@@ -2133,13 +2129,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
-        <v>10022</v>
+        <v>10024</v>
       </c>
       <c r="B56" s="5">
         <v>1</v>
       </c>
       <c r="C56" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -2162,13 +2158,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
-        <v>10023</v>
+        <v>10025</v>
       </c>
       <c r="B57" s="5">
         <v>1</v>
       </c>
       <c r="C57" s="5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -2191,13 +2187,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
-        <v>10024</v>
+        <v>10026</v>
       </c>
       <c r="B58" s="5">
         <v>1</v>
       </c>
       <c r="C58" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -2220,13 +2216,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
-        <v>10025</v>
+        <v>10027</v>
       </c>
       <c r="B59" s="5">
         <v>1</v>
       </c>
       <c r="C59" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -2249,13 +2245,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
-        <v>10026</v>
+        <v>10028</v>
       </c>
       <c r="B60" s="5">
         <v>1</v>
       </c>
       <c r="C60" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s">
         <v>17</v>
@@ -2278,13 +2274,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
-        <v>10027</v>
+        <v>10029</v>
       </c>
       <c r="B61" s="5">
         <v>1</v>
       </c>
       <c r="C61" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D61" t="s">
         <v>17</v>
@@ -2307,13 +2303,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
-        <v>10028</v>
+        <v>10030</v>
       </c>
       <c r="B62" s="5">
         <v>1</v>
       </c>
       <c r="C62" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D62" t="s">
         <v>17</v>
@@ -2335,191 +2331,191 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63" s="5">
-        <v>10029</v>
-      </c>
-      <c r="B63" s="5">
-        <v>1</v>
-      </c>
-      <c r="C63" s="5">
-        <v>29</v>
-      </c>
-      <c r="D63" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" t="s">
-        <v>19</v>
-      </c>
-      <c r="H63" t="s">
-        <v>19</v>
-      </c>
-      <c r="I63" t="s">
-        <v>19</v>
+      <c r="A63" s="6">
+        <v>10010002</v>
+      </c>
+      <c r="B63" s="6">
+        <v>1001</v>
+      </c>
+      <c r="C63" s="6">
+        <v>2</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A64" s="5">
-        <v>10030</v>
-      </c>
-      <c r="B64" s="5">
-        <v>1</v>
-      </c>
-      <c r="C64" s="5">
-        <v>30</v>
-      </c>
-      <c r="D64" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" t="s">
-        <v>18</v>
-      </c>
-      <c r="F64" t="s">
-        <v>19</v>
-      </c>
-      <c r="G64" t="s">
-        <v>19</v>
-      </c>
-      <c r="H64" t="s">
-        <v>19</v>
-      </c>
-      <c r="I64" t="s">
-        <v>19</v>
+      <c r="A64" s="6">
+        <v>10010003</v>
+      </c>
+      <c r="B64" s="6">
+        <v>1001</v>
+      </c>
+      <c r="C64" s="6">
+        <v>3</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
-        <v>10010001</v>
+        <v>10010004</v>
       </c>
       <c r="B65" s="6">
         <v>1001</v>
       </c>
       <c r="C65" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
-        <v>10010002</v>
+        <v>10010005</v>
       </c>
       <c r="B66" s="6">
         <v>1001</v>
       </c>
       <c r="C66" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
-        <v>10010003</v>
+        <v>10010006</v>
       </c>
       <c r="B67" s="6">
         <v>1001</v>
       </c>
       <c r="C67" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
-        <v>10010004</v>
+        <v>10010007</v>
       </c>
       <c r="B68" s="6">
         <v>1001</v>
       </c>
       <c r="C68" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
-        <v>10010005</v>
+        <v>10010008</v>
       </c>
       <c r="B69" s="6">
         <v>1001</v>
       </c>
       <c r="C69" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>16</v>
@@ -2539,13 +2535,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
-        <v>10010006</v>
+        <v>10010009</v>
       </c>
       <c r="B70" s="6">
         <v>1001</v>
       </c>
       <c r="C70" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>27</v>
@@ -2568,13 +2564,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
-        <v>10010007</v>
+        <v>10010010</v>
       </c>
       <c r="B71" s="6">
         <v>1001</v>
       </c>
       <c r="C71" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>27</v>
@@ -2597,13 +2593,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
-        <v>10010008</v>
+        <v>10010011</v>
       </c>
       <c r="B72" s="6">
         <v>1001</v>
       </c>
       <c r="C72" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>27</v>
@@ -2626,13 +2622,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
-        <v>10010009</v>
+        <v>10010012</v>
       </c>
       <c r="B73" s="6">
         <v>1001</v>
       </c>
       <c r="C73" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>27</v>
@@ -2655,13 +2651,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
-        <v>10010010</v>
+        <v>10010013</v>
       </c>
       <c r="B74" s="6">
         <v>1001</v>
       </c>
       <c r="C74" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>27</v>
@@ -2684,13 +2680,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
-        <v>10010011</v>
+        <v>10010014</v>
       </c>
       <c r="B75" s="6">
         <v>1001</v>
       </c>
       <c r="C75" s="6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>27</v>
@@ -2713,13 +2709,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
-        <v>10010012</v>
+        <v>10010015</v>
       </c>
       <c r="B76" s="6">
         <v>1001</v>
       </c>
       <c r="C76" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>27</v>
@@ -2742,13 +2738,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
-        <v>10010013</v>
+        <v>10010016</v>
       </c>
       <c r="B77" s="6">
         <v>1001</v>
       </c>
       <c r="C77" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>27</v>
@@ -2771,13 +2767,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
-        <v>10010014</v>
+        <v>10010017</v>
       </c>
       <c r="B78" s="6">
         <v>1001</v>
       </c>
       <c r="C78" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>27</v>
@@ -2800,13 +2796,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
-        <v>10010015</v>
+        <v>10010018</v>
       </c>
       <c r="B79" s="6">
         <v>1001</v>
       </c>
       <c r="C79" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>27</v>
@@ -2829,13 +2825,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
-        <v>10010016</v>
+        <v>10010019</v>
       </c>
       <c r="B80" s="6">
         <v>1001</v>
       </c>
       <c r="C80" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>27</v>
@@ -2858,13 +2854,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
-        <v>10010017</v>
+        <v>10010020</v>
       </c>
       <c r="B81" s="6">
         <v>1001</v>
       </c>
       <c r="C81" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>27</v>
@@ -2887,13 +2883,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
-        <v>10010018</v>
+        <v>10010021</v>
       </c>
       <c r="B82" s="6">
         <v>1001</v>
       </c>
       <c r="C82" s="6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>27</v>
@@ -2916,13 +2912,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
-        <v>10010019</v>
+        <v>10010022</v>
       </c>
       <c r="B83" s="6">
         <v>1001</v>
       </c>
       <c r="C83" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>27</v>
@@ -2945,13 +2941,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
-        <v>10010020</v>
+        <v>10010023</v>
       </c>
       <c r="B84" s="6">
         <v>1001</v>
       </c>
       <c r="C84" s="6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>27</v>
@@ -2974,13 +2970,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
-        <v>10010021</v>
+        <v>10010024</v>
       </c>
       <c r="B85" s="6">
         <v>1001</v>
       </c>
       <c r="C85" s="6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>27</v>
@@ -3003,13 +2999,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
-        <v>10010022</v>
+        <v>10010025</v>
       </c>
       <c r="B86" s="6">
         <v>1001</v>
       </c>
       <c r="C86" s="6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>27</v>
@@ -3032,13 +3028,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
-        <v>10010023</v>
+        <v>10010026</v>
       </c>
       <c r="B87" s="6">
         <v>1001</v>
       </c>
       <c r="C87" s="6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>27</v>
@@ -3061,13 +3057,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
-        <v>10010024</v>
+        <v>10010027</v>
       </c>
       <c r="B88" s="6">
         <v>1001</v>
       </c>
       <c r="C88" s="6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>27</v>
@@ -3090,13 +3086,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
-        <v>10010025</v>
+        <v>10010028</v>
       </c>
       <c r="B89" s="6">
         <v>1001</v>
       </c>
       <c r="C89" s="6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>27</v>
@@ -3119,13 +3115,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
-        <v>10010026</v>
+        <v>10010029</v>
       </c>
       <c r="B90" s="6">
         <v>1001</v>
       </c>
       <c r="C90" s="6">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>27</v>
@@ -3148,13 +3144,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
-        <v>10010027</v>
+        <v>10010030</v>
       </c>
       <c r="B91" s="6">
         <v>1001</v>
       </c>
       <c r="C91" s="6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>27</v>
@@ -3176,101 +3172,101 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A92" s="6">
-        <v>10010028</v>
-      </c>
-      <c r="B92" s="6">
-        <v>1001</v>
-      </c>
-      <c r="C92" s="6">
-        <v>28</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>16</v>
+      <c r="A92" s="7">
+        <v>10020002</v>
+      </c>
+      <c r="B92" s="7">
+        <v>1002</v>
+      </c>
+      <c r="C92" s="7">
+        <v>2</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A93" s="6">
-        <v>10010029</v>
-      </c>
-      <c r="B93" s="6">
-        <v>1001</v>
-      </c>
-      <c r="C93" s="6">
-        <v>29</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>16</v>
+      <c r="A93" s="7">
+        <v>10020003</v>
+      </c>
+      <c r="B93" s="7">
+        <v>1002</v>
+      </c>
+      <c r="C93" s="7">
+        <v>3</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A94" s="6">
-        <v>10010030</v>
-      </c>
-      <c r="B94" s="6">
-        <v>1001</v>
-      </c>
-      <c r="C94" s="6">
-        <v>30</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>16</v>
+      <c r="A94" s="7">
+        <v>10020004</v>
+      </c>
+      <c r="B94" s="7">
+        <v>1002</v>
+      </c>
+      <c r="C94" s="7">
+        <v>4</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
-        <v>10020001</v>
+        <v>10020005</v>
       </c>
       <c r="B95" s="7">
         <v>1002</v>
       </c>
       <c r="C95" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>29</v>
@@ -3293,13 +3289,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
-        <v>10020002</v>
+        <v>10020006</v>
       </c>
       <c r="B96" s="7">
         <v>1002</v>
       </c>
       <c r="C96" s="7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>29</v>
@@ -3322,13 +3318,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
-        <v>10020003</v>
+        <v>10020007</v>
       </c>
       <c r="B97" s="7">
         <v>1002</v>
       </c>
       <c r="C97" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>29</v>
@@ -3351,13 +3347,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
-        <v>10020004</v>
+        <v>10020008</v>
       </c>
       <c r="B98" s="7">
         <v>1002</v>
       </c>
       <c r="C98" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>29</v>
@@ -3380,13 +3376,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
-        <v>10020005</v>
+        <v>10020009</v>
       </c>
       <c r="B99" s="7">
         <v>1002</v>
       </c>
       <c r="C99" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>29</v>
@@ -3409,13 +3405,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
-        <v>10020006</v>
+        <v>10020010</v>
       </c>
       <c r="B100" s="7">
         <v>1002</v>
       </c>
       <c r="C100" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>29</v>
@@ -3438,13 +3434,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
-        <v>10020007</v>
+        <v>10020011</v>
       </c>
       <c r="B101" s="7">
         <v>1002</v>
       </c>
       <c r="C101" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>29</v>
@@ -3467,13 +3463,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
-        <v>10020008</v>
+        <v>10020012</v>
       </c>
       <c r="B102" s="7">
         <v>1002</v>
       </c>
       <c r="C102" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>29</v>
@@ -3496,13 +3492,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
-        <v>10020009</v>
+        <v>10020013</v>
       </c>
       <c r="B103" s="7">
         <v>1002</v>
       </c>
       <c r="C103" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>29</v>
@@ -3525,13 +3521,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
-        <v>10020010</v>
+        <v>10020014</v>
       </c>
       <c r="B104" s="7">
         <v>1002</v>
       </c>
       <c r="C104" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>29</v>
@@ -3554,13 +3550,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
-        <v>10020011</v>
+        <v>10020015</v>
       </c>
       <c r="B105" s="7">
         <v>1002</v>
       </c>
       <c r="C105" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>29</v>
@@ -3583,13 +3579,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
-        <v>10020012</v>
+        <v>10020016</v>
       </c>
       <c r="B106" s="7">
         <v>1002</v>
       </c>
       <c r="C106" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>29</v>
@@ -3612,13 +3608,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
-        <v>10020013</v>
+        <v>10020017</v>
       </c>
       <c r="B107" s="7">
         <v>1002</v>
       </c>
       <c r="C107" s="7">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>29</v>
@@ -3641,13 +3637,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
-        <v>10020014</v>
+        <v>10020018</v>
       </c>
       <c r="B108" s="7">
         <v>1002</v>
       </c>
       <c r="C108" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>29</v>
@@ -3670,13 +3666,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
-        <v>10020015</v>
+        <v>10020019</v>
       </c>
       <c r="B109" s="7">
         <v>1002</v>
       </c>
       <c r="C109" s="7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>29</v>
@@ -3699,13 +3695,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
-        <v>10020016</v>
+        <v>10020020</v>
       </c>
       <c r="B110" s="7">
         <v>1002</v>
       </c>
       <c r="C110" s="7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>29</v>
@@ -3728,13 +3724,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
-        <v>10020017</v>
+        <v>10020021</v>
       </c>
       <c r="B111" s="7">
         <v>1002</v>
       </c>
       <c r="C111" s="7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>29</v>
@@ -3757,13 +3753,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
-        <v>10020018</v>
+        <v>10020022</v>
       </c>
       <c r="B112" s="7">
         <v>1002</v>
       </c>
       <c r="C112" s="7">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>29</v>
@@ -3786,13 +3782,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="7">
-        <v>10020019</v>
+        <v>10020023</v>
       </c>
       <c r="B113" s="7">
         <v>1002</v>
       </c>
       <c r="C113" s="7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>29</v>
@@ -3815,13 +3811,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="7">
-        <v>10020020</v>
+        <v>10020024</v>
       </c>
       <c r="B114" s="7">
         <v>1002</v>
       </c>
       <c r="C114" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>29</v>
@@ -3844,13 +3840,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="7">
-        <v>10020021</v>
+        <v>10020025</v>
       </c>
       <c r="B115" s="7">
         <v>1002</v>
       </c>
       <c r="C115" s="7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>29</v>
@@ -3873,13 +3869,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="7">
-        <v>10020022</v>
+        <v>10020026</v>
       </c>
       <c r="B116" s="7">
         <v>1002</v>
       </c>
       <c r="C116" s="7">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>29</v>
@@ -3902,13 +3898,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="7">
-        <v>10020023</v>
+        <v>10020027</v>
       </c>
       <c r="B117" s="7">
         <v>1002</v>
       </c>
       <c r="C117" s="7">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>29</v>
@@ -3931,13 +3927,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="7">
-        <v>10020024</v>
+        <v>10020028</v>
       </c>
       <c r="B118" s="7">
         <v>1002</v>
       </c>
       <c r="C118" s="7">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>29</v>
@@ -3960,13 +3956,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="7">
-        <v>10020025</v>
+        <v>10020029</v>
       </c>
       <c r="B119" s="7">
         <v>1002</v>
       </c>
       <c r="C119" s="7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>29</v>
@@ -3989,13 +3985,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="7">
-        <v>10020026</v>
+        <v>10020030</v>
       </c>
       <c r="B120" s="7">
         <v>1002</v>
       </c>
       <c r="C120" s="7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>29</v>
@@ -4017,133 +4013,133 @@
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A121" s="7">
-        <v>10020027</v>
-      </c>
-      <c r="B121" s="7">
-        <v>1002</v>
-      </c>
-      <c r="C121" s="7">
-        <v>27</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>29</v>
+      <c r="A121" s="8">
+        <v>10030002</v>
+      </c>
+      <c r="B121" s="8">
+        <v>1003</v>
+      </c>
+      <c r="C121" s="8">
+        <v>2</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A122" s="7">
-        <v>10020028</v>
-      </c>
-      <c r="B122" s="7">
-        <v>1002</v>
-      </c>
-      <c r="C122" s="7">
-        <v>28</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>29</v>
+      <c r="A122" s="8">
+        <v>10030003</v>
+      </c>
+      <c r="B122" s="8">
+        <v>1003</v>
+      </c>
+      <c r="C122" s="8">
+        <v>3</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A123" s="7">
-        <v>10020029</v>
-      </c>
-      <c r="B123" s="7">
-        <v>1002</v>
-      </c>
-      <c r="C123" s="7">
-        <v>29</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>29</v>
+      <c r="A123" s="8">
+        <v>10030004</v>
+      </c>
+      <c r="B123" s="8">
+        <v>1003</v>
+      </c>
+      <c r="C123" s="8">
+        <v>4</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A124" s="7">
-        <v>10020030</v>
-      </c>
-      <c r="B124" s="7">
-        <v>1002</v>
-      </c>
-      <c r="C124" s="7">
+      <c r="A124" s="8">
+        <v>10030005</v>
+      </c>
+      <c r="B124" s="8">
+        <v>1003</v>
+      </c>
+      <c r="C124" s="8">
+        <v>5</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>29</v>
+      <c r="E124" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="8">
-        <v>10030001</v>
+        <v>10030006</v>
       </c>
       <c r="B125" s="8">
         <v>1003</v>
       </c>
       <c r="C125" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>26</v>
@@ -4163,16 +4159,16 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="8">
-        <v>10030002</v>
+        <v>10030007</v>
       </c>
       <c r="B126" s="8">
         <v>1003</v>
       </c>
       <c r="C126" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>26</v>
@@ -4192,16 +4188,16 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="8">
-        <v>10030003</v>
+        <v>10030008</v>
       </c>
       <c r="B127" s="8">
         <v>1003</v>
       </c>
       <c r="C127" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>26</v>
@@ -4221,16 +4217,16 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="8">
-        <v>10030004</v>
+        <v>10030009</v>
       </c>
       <c r="B128" s="8">
         <v>1003</v>
       </c>
       <c r="C128" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>26</v>
@@ -4250,16 +4246,16 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="8">
-        <v>10030005</v>
+        <v>10030010</v>
       </c>
       <c r="B129" s="8">
         <v>1003</v>
       </c>
       <c r="C129" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>26</v>
@@ -4279,16 +4275,16 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="8">
-        <v>10030006</v>
+        <v>10030011</v>
       </c>
       <c r="B130" s="8">
         <v>1003</v>
       </c>
       <c r="C130" s="8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>26</v>
@@ -4308,16 +4304,16 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="8">
-        <v>10030007</v>
+        <v>10030012</v>
       </c>
       <c r="B131" s="8">
         <v>1003</v>
       </c>
       <c r="C131" s="8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>26</v>
@@ -4337,13 +4333,13 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
-        <v>10030008</v>
+        <v>10030013</v>
       </c>
       <c r="B132" s="8">
         <v>1003</v>
       </c>
       <c r="C132" s="8">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>31</v>
@@ -4366,13 +4362,13 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
-        <v>10030009</v>
+        <v>10030014</v>
       </c>
       <c r="B133" s="8">
         <v>1003</v>
       </c>
       <c r="C133" s="8">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>31</v>
@@ -4395,13 +4391,13 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
-        <v>10030010</v>
+        <v>10030015</v>
       </c>
       <c r="B134" s="8">
         <v>1003</v>
       </c>
       <c r="C134" s="8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>31</v>
@@ -4424,13 +4420,13 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
-        <v>10030011</v>
+        <v>10030016</v>
       </c>
       <c r="B135" s="8">
         <v>1003</v>
       </c>
       <c r="C135" s="8">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>31</v>
@@ -4453,13 +4449,13 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
-        <v>10030012</v>
+        <v>10030017</v>
       </c>
       <c r="B136" s="8">
         <v>1003</v>
       </c>
       <c r="C136" s="8">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>31</v>
@@ -4482,13 +4478,13 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
-        <v>10030013</v>
+        <v>10030018</v>
       </c>
       <c r="B137" s="8">
         <v>1003</v>
       </c>
       <c r="C137" s="8">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>31</v>
@@ -4511,13 +4507,13 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
-        <v>10030014</v>
+        <v>10030019</v>
       </c>
       <c r="B138" s="8">
         <v>1003</v>
       </c>
       <c r="C138" s="8">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>31</v>
@@ -4540,13 +4536,13 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="8">
-        <v>10030015</v>
+        <v>10030020</v>
       </c>
       <c r="B139" s="8">
         <v>1003</v>
       </c>
       <c r="C139" s="8">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>31</v>
@@ -4569,13 +4565,13 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="8">
-        <v>10030016</v>
+        <v>10030021</v>
       </c>
       <c r="B140" s="8">
         <v>1003</v>
       </c>
       <c r="C140" s="8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>31</v>
@@ -4598,13 +4594,13 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="8">
-        <v>10030017</v>
+        <v>10030022</v>
       </c>
       <c r="B141" s="8">
         <v>1003</v>
       </c>
       <c r="C141" s="8">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>31</v>
@@ -4627,13 +4623,13 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="8">
-        <v>10030018</v>
+        <v>10030023</v>
       </c>
       <c r="B142" s="8">
         <v>1003</v>
       </c>
       <c r="C142" s="8">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>31</v>
@@ -4656,13 +4652,13 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="8">
-        <v>10030019</v>
+        <v>10030024</v>
       </c>
       <c r="B143" s="8">
         <v>1003</v>
       </c>
       <c r="C143" s="8">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>31</v>
@@ -4685,13 +4681,13 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="8">
-        <v>10030020</v>
+        <v>10030025</v>
       </c>
       <c r="B144" s="8">
         <v>1003</v>
       </c>
       <c r="C144" s="8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>31</v>
@@ -4714,13 +4710,13 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="8">
-        <v>10030021</v>
+        <v>10030026</v>
       </c>
       <c r="B145" s="8">
         <v>1003</v>
       </c>
       <c r="C145" s="8">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>31</v>
@@ -4743,13 +4739,13 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
-        <v>10030022</v>
+        <v>10030027</v>
       </c>
       <c r="B146" s="8">
         <v>1003</v>
       </c>
       <c r="C146" s="8">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>31</v>
@@ -4772,13 +4768,13 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
-        <v>10030023</v>
+        <v>10030028</v>
       </c>
       <c r="B147" s="8">
         <v>1003</v>
       </c>
       <c r="C147" s="8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>31</v>
@@ -4801,13 +4797,13 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
-        <v>10030024</v>
+        <v>10030029</v>
       </c>
       <c r="B148" s="8">
         <v>1003</v>
       </c>
       <c r="C148" s="8">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>31</v>
@@ -4830,13 +4826,13 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
-        <v>10030025</v>
+        <v>10030030</v>
       </c>
       <c r="B149" s="8">
         <v>1003</v>
       </c>
       <c r="C149" s="8">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>31</v>
@@ -4859,13 +4855,13 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
-        <v>10030026</v>
+        <v>10030031</v>
       </c>
       <c r="B150" s="8">
         <v>1003</v>
       </c>
       <c r="C150" s="8">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>31</v>
@@ -4888,13 +4884,13 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
-        <v>10030027</v>
+        <v>10030032</v>
       </c>
       <c r="B151" s="8">
         <v>1003</v>
       </c>
       <c r="C151" s="8">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>31</v>
@@ -4917,13 +4913,13 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
-        <v>10030028</v>
+        <v>10030033</v>
       </c>
       <c r="B152" s="8">
         <v>1003</v>
       </c>
       <c r="C152" s="8">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>31</v>
@@ -4946,13 +4942,13 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
-        <v>10030029</v>
+        <v>10030034</v>
       </c>
       <c r="B153" s="8">
         <v>1003</v>
       </c>
       <c r="C153" s="8">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>31</v>
@@ -4975,13 +4971,13 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
-        <v>10030030</v>
+        <v>10030035</v>
       </c>
       <c r="B154" s="8">
         <v>1003</v>
       </c>
       <c r="C154" s="8">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>31</v>
@@ -5004,13 +5000,13 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
-        <v>10030031</v>
+        <v>10030036</v>
       </c>
       <c r="B155" s="8">
         <v>1003</v>
       </c>
       <c r="C155" s="8">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>31</v>
@@ -5033,13 +5029,13 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
-        <v>10030032</v>
+        <v>10030037</v>
       </c>
       <c r="B156" s="8">
         <v>1003</v>
       </c>
       <c r="C156" s="8">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>31</v>
@@ -5062,13 +5058,13 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
-        <v>10030033</v>
+        <v>10030038</v>
       </c>
       <c r="B157" s="8">
         <v>1003</v>
       </c>
       <c r="C157" s="8">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>31</v>
@@ -5091,13 +5087,13 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
-        <v>10030034</v>
+        <v>10030039</v>
       </c>
       <c r="B158" s="8">
         <v>1003</v>
       </c>
       <c r="C158" s="8">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>31</v>
@@ -5120,13 +5116,13 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
-        <v>10030035</v>
+        <v>10030040</v>
       </c>
       <c r="B159" s="8">
         <v>1003</v>
       </c>
       <c r="C159" s="8">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>31</v>
@@ -5148,159 +5144,159 @@
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A160" s="8">
-        <v>10030036</v>
-      </c>
-      <c r="B160" s="8">
-        <v>1003</v>
-      </c>
-      <c r="C160" s="8">
-        <v>36</v>
-      </c>
-      <c r="D160" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F160" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G160" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H160" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I160" s="4" t="s">
-        <v>26</v>
+      <c r="A160" s="9">
+        <v>10040002</v>
+      </c>
+      <c r="B160" s="9">
+        <v>1004</v>
+      </c>
+      <c r="C160" s="9">
+        <v>2</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A161" s="8">
-        <v>10030037</v>
-      </c>
-      <c r="B161" s="8">
-        <v>1003</v>
-      </c>
-      <c r="C161" s="8">
-        <v>37</v>
-      </c>
-      <c r="D161" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F161" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G161" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H161" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I161" s="4" t="s">
-        <v>26</v>
+      <c r="A161" s="9">
+        <v>10040003</v>
+      </c>
+      <c r="B161" s="9">
+        <v>1004</v>
+      </c>
+      <c r="C161" s="9">
+        <v>3</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A162" s="8">
-        <v>10030038</v>
-      </c>
-      <c r="B162" s="8">
-        <v>1003</v>
-      </c>
-      <c r="C162" s="8">
-        <v>38</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F162" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G162" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H162" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I162" s="4" t="s">
-        <v>26</v>
+      <c r="A162" s="9">
+        <v>10040004</v>
+      </c>
+      <c r="B162" s="9">
+        <v>1004</v>
+      </c>
+      <c r="C162" s="9">
+        <v>4</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A163" s="8">
-        <v>10030039</v>
-      </c>
-      <c r="B163" s="8">
-        <v>1003</v>
-      </c>
-      <c r="C163" s="8">
-        <v>39</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F163" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G163" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H163" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I163" s="4" t="s">
-        <v>26</v>
+      <c r="A163" s="9">
+        <v>10040005</v>
+      </c>
+      <c r="B163" s="9">
+        <v>1004</v>
+      </c>
+      <c r="C163" s="9">
+        <v>5</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A164" s="8">
-        <v>10030040</v>
-      </c>
-      <c r="B164" s="8">
-        <v>1003</v>
-      </c>
-      <c r="C164" s="8">
-        <v>40</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G164" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H164" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I164" s="4" t="s">
-        <v>26</v>
+      <c r="A164" s="9">
+        <v>10040006</v>
+      </c>
+      <c r="B164" s="9">
+        <v>1004</v>
+      </c>
+      <c r="C164" s="9">
+        <v>6</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="9">
-        <v>10040001</v>
+        <v>10040007</v>
       </c>
       <c r="B165" s="9">
         <v>1004</v>
       </c>
       <c r="C165" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>28</v>
@@ -5323,13 +5319,13 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="9">
-        <v>10040002</v>
+        <v>10040008</v>
       </c>
       <c r="B166" s="9">
         <v>1004</v>
       </c>
       <c r="C166" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>28</v>
@@ -5352,13 +5348,13 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="9">
-        <v>10040003</v>
+        <v>10040009</v>
       </c>
       <c r="B167" s="9">
         <v>1004</v>
       </c>
       <c r="C167" s="9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>28</v>
@@ -5381,13 +5377,13 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="9">
-        <v>10040004</v>
+        <v>10040010</v>
       </c>
       <c r="B168" s="9">
         <v>1004</v>
       </c>
       <c r="C168" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>28</v>
@@ -5410,13 +5406,13 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="9">
-        <v>10040005</v>
+        <v>10040011</v>
       </c>
       <c r="B169" s="9">
         <v>1004</v>
       </c>
       <c r="C169" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>28</v>
@@ -5439,13 +5435,13 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="9">
-        <v>10040006</v>
+        <v>10040012</v>
       </c>
       <c r="B170" s="9">
         <v>1004</v>
       </c>
       <c r="C170" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>28</v>
@@ -5468,13 +5464,13 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="9">
-        <v>10040007</v>
+        <v>10040013</v>
       </c>
       <c r="B171" s="9">
         <v>1004</v>
       </c>
       <c r="C171" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>28</v>
@@ -5497,13 +5493,13 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="9">
-        <v>10040008</v>
+        <v>10040014</v>
       </c>
       <c r="B172" s="9">
         <v>1004</v>
       </c>
       <c r="C172" s="9">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>28</v>
@@ -5526,13 +5522,13 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="9">
-        <v>10040009</v>
+        <v>10040015</v>
       </c>
       <c r="B173" s="9">
         <v>1004</v>
       </c>
       <c r="C173" s="9">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>28</v>
@@ -5555,13 +5551,13 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="9">
-        <v>10040010</v>
+        <v>10040016</v>
       </c>
       <c r="B174" s="9">
         <v>1004</v>
       </c>
       <c r="C174" s="9">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>28</v>
@@ -5584,13 +5580,13 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="9">
-        <v>10040011</v>
+        <v>10040017</v>
       </c>
       <c r="B175" s="9">
         <v>1004</v>
       </c>
       <c r="C175" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>28</v>
@@ -5613,13 +5609,13 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="9">
-        <v>10040012</v>
+        <v>10040018</v>
       </c>
       <c r="B176" s="9">
         <v>1004</v>
       </c>
       <c r="C176" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>28</v>
@@ -5642,13 +5638,13 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="9">
-        <v>10040013</v>
+        <v>10040019</v>
       </c>
       <c r="B177" s="9">
         <v>1004</v>
       </c>
       <c r="C177" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>28</v>
@@ -5671,13 +5667,13 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="9">
-        <v>10040014</v>
+        <v>10040020</v>
       </c>
       <c r="B178" s="9">
         <v>1004</v>
       </c>
       <c r="C178" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>28</v>
@@ -5700,13 +5696,13 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="9">
-        <v>10040015</v>
+        <v>10040021</v>
       </c>
       <c r="B179" s="9">
         <v>1004</v>
       </c>
       <c r="C179" s="9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>28</v>
@@ -5729,13 +5725,13 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="9">
-        <v>10040016</v>
+        <v>10040022</v>
       </c>
       <c r="B180" s="9">
         <v>1004</v>
       </c>
       <c r="C180" s="9">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>28</v>
@@ -5758,13 +5754,13 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="9">
-        <v>10040017</v>
+        <v>10040023</v>
       </c>
       <c r="B181" s="9">
         <v>1004</v>
       </c>
       <c r="C181" s="9">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>28</v>
@@ -5787,13 +5783,13 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="9">
-        <v>10040018</v>
+        <v>10040024</v>
       </c>
       <c r="B182" s="9">
         <v>1004</v>
       </c>
       <c r="C182" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>28</v>
@@ -5816,13 +5812,13 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="9">
-        <v>10040019</v>
+        <v>10040025</v>
       </c>
       <c r="B183" s="9">
         <v>1004</v>
       </c>
       <c r="C183" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>28</v>
@@ -5845,13 +5841,13 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="9">
-        <v>10040020</v>
+        <v>10040026</v>
       </c>
       <c r="B184" s="9">
         <v>1004</v>
       </c>
       <c r="C184" s="9">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>28</v>
@@ -5874,13 +5870,13 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="9">
-        <v>10040021</v>
+        <v>10040027</v>
       </c>
       <c r="B185" s="9">
         <v>1004</v>
       </c>
       <c r="C185" s="9">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D185" s="3" t="s">
         <v>28</v>
@@ -5903,13 +5899,13 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="9">
-        <v>10040022</v>
+        <v>10040028</v>
       </c>
       <c r="B186" s="9">
         <v>1004</v>
       </c>
       <c r="C186" s="9">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>28</v>
@@ -5932,13 +5928,13 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="9">
-        <v>10040023</v>
+        <v>10040029</v>
       </c>
       <c r="B187" s="9">
         <v>1004</v>
       </c>
       <c r="C187" s="9">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D187" s="3" t="s">
         <v>28</v>
@@ -5961,13 +5957,13 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="9">
-        <v>10040024</v>
+        <v>10040030</v>
       </c>
       <c r="B188" s="9">
         <v>1004</v>
       </c>
       <c r="C188" s="9">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>28</v>
@@ -5990,13 +5986,13 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="9">
-        <v>10040025</v>
+        <v>10040031</v>
       </c>
       <c r="B189" s="9">
         <v>1004</v>
       </c>
       <c r="C189" s="9">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>28</v>
@@ -6019,13 +6015,13 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="9">
-        <v>10040026</v>
+        <v>10040032</v>
       </c>
       <c r="B190" s="9">
         <v>1004</v>
       </c>
       <c r="C190" s="9">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>28</v>
@@ -6048,13 +6044,13 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="9">
-        <v>10040027</v>
+        <v>10040033</v>
       </c>
       <c r="B191" s="9">
         <v>1004</v>
       </c>
       <c r="C191" s="9">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>28</v>
@@ -6077,13 +6073,13 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="9">
-        <v>10040028</v>
+        <v>10040034</v>
       </c>
       <c r="B192" s="9">
         <v>1004</v>
       </c>
       <c r="C192" s="9">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>28</v>
@@ -6106,13 +6102,13 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="9">
-        <v>10040029</v>
+        <v>10040035</v>
       </c>
       <c r="B193" s="9">
         <v>1004</v>
       </c>
       <c r="C193" s="9">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>28</v>
@@ -6135,13 +6131,13 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="9">
-        <v>10040030</v>
+        <v>10040036</v>
       </c>
       <c r="B194" s="9">
         <v>1004</v>
       </c>
       <c r="C194" s="9">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D194" s="3" t="s">
         <v>28</v>
@@ -6164,13 +6160,13 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="9">
-        <v>10040031</v>
+        <v>10040037</v>
       </c>
       <c r="B195" s="9">
         <v>1004</v>
       </c>
       <c r="C195" s="9">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>28</v>
@@ -6193,13 +6189,13 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="9">
-        <v>10040032</v>
+        <v>10040038</v>
       </c>
       <c r="B196" s="9">
         <v>1004</v>
       </c>
       <c r="C196" s="9">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>28</v>
@@ -6222,13 +6218,13 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="9">
-        <v>10040033</v>
+        <v>10040039</v>
       </c>
       <c r="B197" s="9">
         <v>1004</v>
       </c>
       <c r="C197" s="9">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>28</v>
@@ -6251,13 +6247,13 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="9">
-        <v>10040034</v>
+        <v>10040040</v>
       </c>
       <c r="B198" s="9">
         <v>1004</v>
       </c>
       <c r="C198" s="9">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>28</v>
@@ -6279,191 +6275,191 @@
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A199" s="9">
-        <v>10040035</v>
-      </c>
-      <c r="B199" s="9">
-        <v>1004</v>
-      </c>
-      <c r="C199" s="9">
-        <v>35</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E199" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H199" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I199" s="3" t="s">
-        <v>28</v>
+      <c r="A199" s="5">
+        <v>1010002</v>
+      </c>
+      <c r="B199" s="5">
+        <v>101</v>
+      </c>
+      <c r="C199" s="5">
+        <v>2</v>
+      </c>
+      <c r="D199" t="s">
+        <v>32</v>
+      </c>
+      <c r="E199" t="s">
+        <v>32</v>
+      </c>
+      <c r="F199" t="s">
+        <v>32</v>
+      </c>
+      <c r="G199" t="s">
+        <v>32</v>
+      </c>
+      <c r="H199" t="s">
+        <v>32</v>
+      </c>
+      <c r="I199" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A200" s="9">
-        <v>10040036</v>
-      </c>
-      <c r="B200" s="9">
-        <v>1004</v>
-      </c>
-      <c r="C200" s="9">
-        <v>36</v>
-      </c>
-      <c r="D200" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E200" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F200" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G200" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H200" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I200" s="3" t="s">
-        <v>28</v>
+      <c r="A200" s="5">
+        <v>1010003</v>
+      </c>
+      <c r="B200" s="5">
+        <v>101</v>
+      </c>
+      <c r="C200" s="5">
+        <v>3</v>
+      </c>
+      <c r="D200" t="s">
+        <v>32</v>
+      </c>
+      <c r="E200" t="s">
+        <v>32</v>
+      </c>
+      <c r="F200" t="s">
+        <v>32</v>
+      </c>
+      <c r="G200" t="s">
+        <v>32</v>
+      </c>
+      <c r="H200" t="s">
+        <v>32</v>
+      </c>
+      <c r="I200" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A201" s="9">
-        <v>10040037</v>
-      </c>
-      <c r="B201" s="9">
-        <v>1004</v>
-      </c>
-      <c r="C201" s="9">
-        <v>37</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E201" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G201" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H201" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I201" s="3" t="s">
-        <v>28</v>
+      <c r="A201" s="5">
+        <v>1010004</v>
+      </c>
+      <c r="B201" s="5">
+        <v>101</v>
+      </c>
+      <c r="C201" s="5">
+        <v>4</v>
+      </c>
+      <c r="D201" t="s">
+        <v>32</v>
+      </c>
+      <c r="E201" t="s">
+        <v>32</v>
+      </c>
+      <c r="F201" t="s">
+        <v>32</v>
+      </c>
+      <c r="G201" t="s">
+        <v>32</v>
+      </c>
+      <c r="H201" t="s">
+        <v>32</v>
+      </c>
+      <c r="I201" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A202" s="9">
-        <v>10040038</v>
-      </c>
-      <c r="B202" s="9">
-        <v>1004</v>
-      </c>
-      <c r="C202" s="9">
-        <v>38</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E202" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F202" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H202" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I202" s="3" t="s">
-        <v>28</v>
+      <c r="A202" s="5">
+        <v>1010005</v>
+      </c>
+      <c r="B202" s="5">
+        <v>101</v>
+      </c>
+      <c r="C202" s="5">
+        <v>5</v>
+      </c>
+      <c r="D202" t="s">
+        <v>32</v>
+      </c>
+      <c r="E202" t="s">
+        <v>32</v>
+      </c>
+      <c r="F202" t="s">
+        <v>32</v>
+      </c>
+      <c r="G202" t="s">
+        <v>32</v>
+      </c>
+      <c r="H202" t="s">
+        <v>32</v>
+      </c>
+      <c r="I202" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A203" s="9">
-        <v>10040039</v>
-      </c>
-      <c r="B203" s="9">
-        <v>1004</v>
-      </c>
-      <c r="C203" s="9">
-        <v>39</v>
-      </c>
-      <c r="D203" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E203" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F203" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G203" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H203" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I203" s="3" t="s">
-        <v>28</v>
+      <c r="A203" s="5">
+        <v>1010006</v>
+      </c>
+      <c r="B203" s="5">
+        <v>101</v>
+      </c>
+      <c r="C203" s="5">
+        <v>6</v>
+      </c>
+      <c r="D203" t="s">
+        <v>32</v>
+      </c>
+      <c r="E203" t="s">
+        <v>32</v>
+      </c>
+      <c r="F203" t="s">
+        <v>32</v>
+      </c>
+      <c r="G203" t="s">
+        <v>32</v>
+      </c>
+      <c r="H203" t="s">
+        <v>32</v>
+      </c>
+      <c r="I203" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A204" s="9">
-        <v>10040040</v>
-      </c>
-      <c r="B204" s="9">
-        <v>1004</v>
-      </c>
-      <c r="C204" s="9">
-        <v>40</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E204" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F204" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H204" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I204" s="3" t="s">
-        <v>28</v>
+      <c r="A204" s="5">
+        <v>1010007</v>
+      </c>
+      <c r="B204" s="5">
+        <v>101</v>
+      </c>
+      <c r="C204" s="5">
+        <v>7</v>
+      </c>
+      <c r="D204" t="s">
+        <v>32</v>
+      </c>
+      <c r="E204" t="s">
+        <v>32</v>
+      </c>
+      <c r="F204" t="s">
+        <v>32</v>
+      </c>
+      <c r="G204" t="s">
+        <v>32</v>
+      </c>
+      <c r="H204" t="s">
+        <v>32</v>
+      </c>
+      <c r="I204" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="5">
-        <v>1010001</v>
+        <v>1010008</v>
       </c>
       <c r="B205" s="5">
         <v>101</v>
       </c>
       <c r="C205" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D205" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E205" t="s">
         <v>32</v>
@@ -6483,13 +6479,13 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="5">
-        <v>1010002</v>
+        <v>1010009</v>
       </c>
       <c r="B206" s="5">
         <v>101</v>
       </c>
       <c r="C206" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D206" t="s">
         <v>32</v>
@@ -6512,13 +6508,13 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="5">
-        <v>1010003</v>
+        <v>1010010</v>
       </c>
       <c r="B207" s="5">
         <v>101</v>
       </c>
       <c r="C207" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D207" t="s">
         <v>32</v>
@@ -6541,13 +6537,13 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="5">
-        <v>1010004</v>
+        <v>1010011</v>
       </c>
       <c r="B208" s="5">
         <v>101</v>
       </c>
       <c r="C208" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D208" t="s">
         <v>32</v>
@@ -6570,13 +6566,13 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="5">
-        <v>1010005</v>
+        <v>1010012</v>
       </c>
       <c r="B209" s="5">
         <v>101</v>
       </c>
       <c r="C209" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D209" t="s">
         <v>32</v>
@@ -6599,13 +6595,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="5">
-        <v>1010006</v>
+        <v>1010013</v>
       </c>
       <c r="B210" s="5">
         <v>101</v>
       </c>
       <c r="C210" s="5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D210" t="s">
         <v>32</v>
@@ -6628,13 +6624,13 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="5">
-        <v>1010007</v>
+        <v>1010014</v>
       </c>
       <c r="B211" s="5">
         <v>101</v>
       </c>
       <c r="C211" s="5">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D211" t="s">
         <v>32</v>
@@ -6657,13 +6653,13 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="5">
-        <v>1010008</v>
+        <v>1010015</v>
       </c>
       <c r="B212" s="5">
         <v>101</v>
       </c>
       <c r="C212" s="5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D212" t="s">
         <v>32</v>
@@ -6686,13 +6682,13 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="5">
-        <v>1010009</v>
+        <v>1010016</v>
       </c>
       <c r="B213" s="5">
         <v>101</v>
       </c>
       <c r="C213" s="5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D213" t="s">
         <v>32</v>
@@ -6715,13 +6711,13 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="5">
-        <v>1010010</v>
+        <v>1010017</v>
       </c>
       <c r="B214" s="5">
         <v>101</v>
       </c>
       <c r="C214" s="5">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D214" t="s">
         <v>32</v>
@@ -6744,13 +6740,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="5">
-        <v>1010011</v>
+        <v>1010018</v>
       </c>
       <c r="B215" s="5">
         <v>101</v>
       </c>
       <c r="C215" s="5">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D215" t="s">
         <v>32</v>
@@ -6773,13 +6769,13 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="5">
-        <v>1010012</v>
+        <v>1010019</v>
       </c>
       <c r="B216" s="5">
         <v>101</v>
       </c>
       <c r="C216" s="5">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D216" t="s">
         <v>32</v>
@@ -6802,13 +6798,13 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="5">
-        <v>1010013</v>
+        <v>1010020</v>
       </c>
       <c r="B217" s="5">
         <v>101</v>
       </c>
       <c r="C217" s="5">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D217" t="s">
         <v>32</v>
@@ -6831,13 +6827,13 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="5">
-        <v>1010014</v>
+        <v>1010021</v>
       </c>
       <c r="B218" s="5">
         <v>101</v>
       </c>
       <c r="C218" s="5">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D218" t="s">
         <v>32</v>
@@ -6860,13 +6856,13 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="5">
-        <v>1010015</v>
+        <v>1010022</v>
       </c>
       <c r="B219" s="5">
         <v>101</v>
       </c>
       <c r="C219" s="5">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D219" t="s">
         <v>32</v>
@@ -6889,13 +6885,13 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="5">
-        <v>1010016</v>
+        <v>1010023</v>
       </c>
       <c r="B220" s="5">
         <v>101</v>
       </c>
       <c r="C220" s="5">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D220" t="s">
         <v>32</v>
@@ -6918,13 +6914,13 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="5">
-        <v>1010017</v>
+        <v>1010024</v>
       </c>
       <c r="B221" s="5">
         <v>101</v>
       </c>
       <c r="C221" s="5">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D221" t="s">
         <v>32</v>
@@ -6947,13 +6943,13 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="5">
-        <v>1010018</v>
+        <v>1010025</v>
       </c>
       <c r="B222" s="5">
         <v>101</v>
       </c>
       <c r="C222" s="5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D222" t="s">
         <v>32</v>
@@ -6976,13 +6972,13 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="5">
-        <v>1010019</v>
+        <v>1010026</v>
       </c>
       <c r="B223" s="5">
         <v>101</v>
       </c>
       <c r="C223" s="5">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D223" t="s">
         <v>32</v>
@@ -7005,13 +7001,13 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="5">
-        <v>1010020</v>
+        <v>1010027</v>
       </c>
       <c r="B224" s="5">
         <v>101</v>
       </c>
       <c r="C224" s="5">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D224" t="s">
         <v>32</v>
@@ -7034,13 +7030,13 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="5">
-        <v>1010021</v>
+        <v>1010028</v>
       </c>
       <c r="B225" s="5">
         <v>101</v>
       </c>
       <c r="C225" s="5">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D225" t="s">
         <v>32</v>
@@ -7063,13 +7059,13 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="5">
-        <v>1010022</v>
+        <v>1010029</v>
       </c>
       <c r="B226" s="5">
         <v>101</v>
       </c>
       <c r="C226" s="5">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D226" t="s">
         <v>32</v>
@@ -7092,13 +7088,13 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="5">
-        <v>1010023</v>
+        <v>1010030</v>
       </c>
       <c r="B227" s="5">
         <v>101</v>
       </c>
       <c r="C227" s="5">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D227" t="s">
         <v>32</v>
@@ -7121,13 +7117,13 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="5">
-        <v>1010024</v>
+        <v>1010031</v>
       </c>
       <c r="B228" s="5">
         <v>101</v>
       </c>
       <c r="C228" s="5">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D228" t="s">
         <v>32</v>
@@ -7150,13 +7146,13 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="5">
-        <v>1010025</v>
+        <v>1010032</v>
       </c>
       <c r="B229" s="5">
         <v>101</v>
       </c>
       <c r="C229" s="5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D229" t="s">
         <v>32</v>
@@ -7179,13 +7175,13 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="5">
-        <v>1010026</v>
+        <v>1010033</v>
       </c>
       <c r="B230" s="5">
         <v>101</v>
       </c>
       <c r="C230" s="5">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D230" t="s">
         <v>32</v>
@@ -7208,13 +7204,13 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="5">
-        <v>1010027</v>
+        <v>1010034</v>
       </c>
       <c r="B231" s="5">
         <v>101</v>
       </c>
       <c r="C231" s="5">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D231" t="s">
         <v>32</v>
@@ -7237,13 +7233,13 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="5">
-        <v>1010028</v>
+        <v>1010035</v>
       </c>
       <c r="B232" s="5">
         <v>101</v>
       </c>
       <c r="C232" s="5">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D232" t="s">
         <v>32</v>
@@ -7266,13 +7262,13 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="5">
-        <v>1010029</v>
+        <v>1010036</v>
       </c>
       <c r="B233" s="5">
         <v>101</v>
       </c>
       <c r="C233" s="5">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D233" t="s">
         <v>32</v>
@@ -7295,13 +7291,13 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="5">
-        <v>1010030</v>
+        <v>1010037</v>
       </c>
       <c r="B234" s="5">
         <v>101</v>
       </c>
       <c r="C234" s="5">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D234" t="s">
         <v>32</v>
@@ -7324,13 +7320,13 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="5">
-        <v>1010031</v>
+        <v>1010038</v>
       </c>
       <c r="B235" s="5">
         <v>101</v>
       </c>
       <c r="C235" s="5">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D235" t="s">
         <v>32</v>
@@ -7353,13 +7349,13 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="5">
-        <v>1010032</v>
+        <v>1010039</v>
       </c>
       <c r="B236" s="5">
         <v>101</v>
       </c>
       <c r="C236" s="5">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D236" t="s">
         <v>32</v>
@@ -7382,13 +7378,13 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="5">
-        <v>1010033</v>
+        <v>1010040</v>
       </c>
       <c r="B237" s="5">
         <v>101</v>
       </c>
       <c r="C237" s="5">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D237" t="s">
         <v>32</v>
@@ -7411,13 +7407,13 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="5">
-        <v>1010034</v>
+        <v>1010041</v>
       </c>
       <c r="B238" s="5">
         <v>101</v>
       </c>
       <c r="C238" s="5">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D238" t="s">
         <v>32</v>
@@ -7440,13 +7436,13 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="5">
-        <v>1010035</v>
+        <v>1010042</v>
       </c>
       <c r="B239" s="5">
         <v>101</v>
       </c>
       <c r="C239" s="5">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D239" t="s">
         <v>32</v>
@@ -7469,13 +7465,13 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="5">
-        <v>1010036</v>
+        <v>1010043</v>
       </c>
       <c r="B240" s="5">
         <v>101</v>
       </c>
       <c r="C240" s="5">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D240" t="s">
         <v>32</v>
@@ -7498,13 +7494,13 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="5">
-        <v>1010037</v>
+        <v>1010044</v>
       </c>
       <c r="B241" s="5">
         <v>101</v>
       </c>
       <c r="C241" s="5">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D241" t="s">
         <v>32</v>
@@ -7527,13 +7523,13 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="5">
-        <v>1010038</v>
+        <v>1010045</v>
       </c>
       <c r="B242" s="5">
         <v>101</v>
       </c>
       <c r="C242" s="5">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D242" t="s">
         <v>32</v>
@@ -7556,13 +7552,13 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="5">
-        <v>1010039</v>
+        <v>1010046</v>
       </c>
       <c r="B243" s="5">
         <v>101</v>
       </c>
       <c r="C243" s="5">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D243" t="s">
         <v>32</v>
@@ -7585,13 +7581,13 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="5">
-        <v>1010040</v>
+        <v>1010047</v>
       </c>
       <c r="B244" s="5">
         <v>101</v>
       </c>
       <c r="C244" s="5">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D244" t="s">
         <v>32</v>
@@ -7614,13 +7610,13 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="5">
-        <v>1010041</v>
+        <v>1010048</v>
       </c>
       <c r="B245" s="5">
         <v>101</v>
       </c>
       <c r="C245" s="5">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D245" t="s">
         <v>32</v>
@@ -7643,13 +7639,13 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="5">
-        <v>1010042</v>
+        <v>1010049</v>
       </c>
       <c r="B246" s="5">
         <v>101</v>
       </c>
       <c r="C246" s="5">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D246" t="s">
         <v>32</v>
@@ -7672,13 +7668,13 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="5">
-        <v>1010043</v>
+        <v>1010050</v>
       </c>
       <c r="B247" s="5">
         <v>101</v>
       </c>
       <c r="C247" s="5">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D247" t="s">
         <v>32</v>
@@ -7701,13 +7697,13 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="5">
-        <v>1010044</v>
+        <v>1010051</v>
       </c>
       <c r="B248" s="5">
         <v>101</v>
       </c>
       <c r="C248" s="5">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D248" t="s">
         <v>32</v>
@@ -7730,13 +7726,13 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="5">
-        <v>1010045</v>
+        <v>1010052</v>
       </c>
       <c r="B249" s="5">
         <v>101</v>
       </c>
       <c r="C249" s="5">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D249" t="s">
         <v>32</v>
@@ -7759,13 +7755,13 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="5">
-        <v>1010046</v>
+        <v>1010053</v>
       </c>
       <c r="B250" s="5">
         <v>101</v>
       </c>
       <c r="C250" s="5">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D250" t="s">
         <v>32</v>
@@ -7788,13 +7784,13 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="5">
-        <v>1010047</v>
+        <v>1010054</v>
       </c>
       <c r="B251" s="5">
         <v>101</v>
       </c>
       <c r="C251" s="5">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D251" t="s">
         <v>32</v>
@@ -7817,13 +7813,13 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="5">
-        <v>1010048</v>
+        <v>1010055</v>
       </c>
       <c r="B252" s="5">
         <v>101</v>
       </c>
       <c r="C252" s="5">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D252" t="s">
         <v>32</v>
@@ -7846,13 +7842,13 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="5">
-        <v>1010049</v>
+        <v>1010056</v>
       </c>
       <c r="B253" s="5">
         <v>101</v>
       </c>
       <c r="C253" s="5">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D253" t="s">
         <v>32</v>
@@ -7875,13 +7871,13 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="5">
-        <v>1010050</v>
+        <v>1010057</v>
       </c>
       <c r="B254" s="5">
         <v>101</v>
       </c>
       <c r="C254" s="5">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D254" t="s">
         <v>32</v>
@@ -7904,13 +7900,13 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="5">
-        <v>1010051</v>
+        <v>1010058</v>
       </c>
       <c r="B255" s="5">
         <v>101</v>
       </c>
       <c r="C255" s="5">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D255" t="s">
         <v>32</v>
@@ -7933,13 +7929,13 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="5">
-        <v>1010052</v>
+        <v>1010059</v>
       </c>
       <c r="B256" s="5">
         <v>101</v>
       </c>
       <c r="C256" s="5">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D256" t="s">
         <v>32</v>
@@ -7962,13 +7958,13 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="5">
-        <v>1010053</v>
+        <v>1010060</v>
       </c>
       <c r="B257" s="5">
         <v>101</v>
       </c>
       <c r="C257" s="5">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D257" t="s">
         <v>32</v>
@@ -7991,1724 +7987,1724 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="5">
-        <v>1010054</v>
+        <v>1020002</v>
       </c>
       <c r="B258" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C258" s="5">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="D258" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E258" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F258" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G258" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H258" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I258" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="5">
-        <v>1010055</v>
+        <v>1020003</v>
       </c>
       <c r="B259" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C259" s="5">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="D259" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E259" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F259" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G259" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H259" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I259" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="5">
-        <v>1010056</v>
+        <v>1020004</v>
       </c>
       <c r="B260" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C260" s="5">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="D260" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E260" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F260" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G260" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H260" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I260" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="5">
-        <v>1010057</v>
+        <v>1020005</v>
       </c>
       <c r="B261" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C261" s="5">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D261" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E261" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F261" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G261" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H261" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I261" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="5">
-        <v>1010058</v>
+        <v>1020006</v>
       </c>
       <c r="B262" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C262" s="5">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E262" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F262" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G262" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H262" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I262" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="5">
-        <v>1010059</v>
+        <v>1020007</v>
       </c>
       <c r="B263" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C263" s="5">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="D263" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E263" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F263" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G263" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H263" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I263" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="5">
-        <v>1010060</v>
+        <v>1020008</v>
       </c>
       <c r="B264" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C264" s="5">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="5">
-        <v>1020001</v>
+        <v>1020009</v>
       </c>
       <c r="B265" s="5">
         <v>102</v>
       </c>
       <c r="C265" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D265" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E265" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F265" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G265" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H265" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I265" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="5">
-        <v>1020002</v>
+        <v>1020010</v>
       </c>
       <c r="B266" s="5">
         <v>102</v>
       </c>
       <c r="C266" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D266" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E266" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F266" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G266" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H266" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I266" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="5">
-        <v>1020003</v>
+        <v>1020011</v>
       </c>
       <c r="B267" s="5">
         <v>102</v>
       </c>
       <c r="C267" s="5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D267" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E267" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F267" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G267" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H267" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I267" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="5">
-        <v>1020004</v>
+        <v>1020012</v>
       </c>
       <c r="B268" s="5">
         <v>102</v>
       </c>
       <c r="C268" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D268" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E268" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F268" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G268" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H268" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I268" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="5">
-        <v>1020005</v>
+        <v>1020013</v>
       </c>
       <c r="B269" s="5">
         <v>102</v>
       </c>
       <c r="C269" s="5">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D269" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E269" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F269" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G269" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H269" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I269" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="5">
-        <v>1020006</v>
+        <v>1020014</v>
       </c>
       <c r="B270" s="5">
         <v>102</v>
       </c>
       <c r="C270" s="5">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D270" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E270" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F270" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G270" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H270" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I270" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="5">
-        <v>1020007</v>
+        <v>1020015</v>
       </c>
       <c r="B271" s="5">
         <v>102</v>
       </c>
       <c r="C271" s="5">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D271" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E271" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F271" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G271" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H271" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I271" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="5">
-        <v>1020008</v>
+        <v>1020016</v>
       </c>
       <c r="B272" s="5">
         <v>102</v>
       </c>
       <c r="C272" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D272" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E272" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F272" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G272" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H272" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I272" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" s="5">
-        <v>1020009</v>
+        <v>1020017</v>
       </c>
       <c r="B273" s="5">
         <v>102</v>
       </c>
       <c r="C273" s="5">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D273" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E273" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F273" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G273" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H273" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I273" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" s="5">
-        <v>1020010</v>
+        <v>1020018</v>
       </c>
       <c r="B274" s="5">
         <v>102</v>
       </c>
       <c r="C274" s="5">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D274" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E274" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F274" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G274" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H274" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I274" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" s="5">
-        <v>1020011</v>
+        <v>1020019</v>
       </c>
       <c r="B275" s="5">
         <v>102</v>
       </c>
       <c r="C275" s="5">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D275" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E275" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F275" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G275" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H275" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I275" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" s="5">
-        <v>1020012</v>
+        <v>1020020</v>
       </c>
       <c r="B276" s="5">
         <v>102</v>
       </c>
       <c r="C276" s="5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D276" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E276" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F276" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G276" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H276" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I276" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" s="5">
-        <v>1020013</v>
+        <v>1020021</v>
       </c>
       <c r="B277" s="5">
         <v>102</v>
       </c>
       <c r="C277" s="5">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D277" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E277" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F277" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G277" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H277" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I277" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" s="5">
-        <v>1020014</v>
+        <v>1020022</v>
       </c>
       <c r="B278" s="5">
         <v>102</v>
       </c>
       <c r="C278" s="5">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D278" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E278" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F278" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G278" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H278" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I278" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" s="5">
-        <v>1020015</v>
+        <v>1020023</v>
       </c>
       <c r="B279" s="5">
         <v>102</v>
       </c>
       <c r="C279" s="5">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D279" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E279" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F279" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G279" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H279" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I279" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" s="5">
-        <v>1020016</v>
+        <v>1020024</v>
       </c>
       <c r="B280" s="5">
         <v>102</v>
       </c>
       <c r="C280" s="5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D280" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E280" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F280" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G280" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H280" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I280" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" s="5">
-        <v>1020017</v>
+        <v>1020025</v>
       </c>
       <c r="B281" s="5">
         <v>102</v>
       </c>
       <c r="C281" s="5">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E281" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F281" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G281" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H281" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I281" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" s="5">
-        <v>1020018</v>
+        <v>1020026</v>
       </c>
       <c r="B282" s="5">
         <v>102</v>
       </c>
       <c r="C282" s="5">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D282" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E282" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F282" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G282" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H282" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I282" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" s="5">
-        <v>1020019</v>
+        <v>1020027</v>
       </c>
       <c r="B283" s="5">
         <v>102</v>
       </c>
       <c r="C283" s="5">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D283" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E283" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F283" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G283" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H283" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I283" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" s="5">
-        <v>1020020</v>
+        <v>1020028</v>
       </c>
       <c r="B284" s="5">
         <v>102</v>
       </c>
       <c r="C284" s="5">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D284" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E284" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F284" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G284" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H284" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I284" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" s="5">
-        <v>1020021</v>
+        <v>1020029</v>
       </c>
       <c r="B285" s="5">
         <v>102</v>
       </c>
       <c r="C285" s="5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D285" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E285" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F285" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G285" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H285" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I285" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" s="5">
-        <v>1020022</v>
+        <v>1020030</v>
       </c>
       <c r="B286" s="5">
         <v>102</v>
       </c>
       <c r="C286" s="5">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D286" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E286" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F286" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G286" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H286" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I286" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" s="5">
-        <v>1020023</v>
+        <v>1020031</v>
       </c>
       <c r="B287" s="5">
         <v>102</v>
       </c>
       <c r="C287" s="5">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D287" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E287" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F287" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G287" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H287" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I287" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" s="5">
-        <v>1020024</v>
+        <v>1020032</v>
       </c>
       <c r="B288" s="5">
         <v>102</v>
       </c>
       <c r="C288" s="5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D288" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E288" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F288" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G288" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H288" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I288" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="5">
-        <v>1020025</v>
+        <v>1020033</v>
       </c>
       <c r="B289" s="5">
         <v>102</v>
       </c>
       <c r="C289" s="5">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D289" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E289" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F289" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G289" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H289" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I289" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" s="5">
-        <v>1020026</v>
+        <v>1020034</v>
       </c>
       <c r="B290" s="5">
         <v>102</v>
       </c>
       <c r="C290" s="5">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D290" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E290" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F290" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G290" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H290" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I290" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" s="5">
-        <v>1020027</v>
+        <v>1020035</v>
       </c>
       <c r="B291" s="5">
         <v>102</v>
       </c>
       <c r="C291" s="5">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D291" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E291" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F291" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G291" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H291" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I291" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="5">
-        <v>1020028</v>
+        <v>1020036</v>
       </c>
       <c r="B292" s="5">
         <v>102</v>
       </c>
       <c r="C292" s="5">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D292" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E292" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F292" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G292" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H292" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I292" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" s="5">
-        <v>1020029</v>
+        <v>1020037</v>
       </c>
       <c r="B293" s="5">
         <v>102</v>
       </c>
       <c r="C293" s="5">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D293" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E293" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F293" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G293" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H293" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I293" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" s="5">
-        <v>1020030</v>
+        <v>1020038</v>
       </c>
       <c r="B294" s="5">
         <v>102</v>
       </c>
       <c r="C294" s="5">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D294" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E294" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F294" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G294" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H294" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I294" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" s="5">
-        <v>1020031</v>
+        <v>1020039</v>
       </c>
       <c r="B295" s="5">
         <v>102</v>
       </c>
       <c r="C295" s="5">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D295" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E295" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F295" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G295" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H295" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I295" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" s="5">
-        <v>1020032</v>
+        <v>1020040</v>
       </c>
       <c r="B296" s="5">
         <v>102</v>
       </c>
       <c r="C296" s="5">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D296" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E296" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F296" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G296" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H296" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I296" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" s="5">
-        <v>1020033</v>
+        <v>1020041</v>
       </c>
       <c r="B297" s="5">
         <v>102</v>
       </c>
       <c r="C297" s="5">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D297" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E297" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F297" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G297" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H297" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I297" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" s="5">
-        <v>1020034</v>
+        <v>1020042</v>
       </c>
       <c r="B298" s="5">
         <v>102</v>
       </c>
       <c r="C298" s="5">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D298" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E298" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F298" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G298" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H298" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I298" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" s="5">
-        <v>1020035</v>
+        <v>1020043</v>
       </c>
       <c r="B299" s="5">
         <v>102</v>
       </c>
       <c r="C299" s="5">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D299" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E299" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F299" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G299" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H299" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I299" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" s="5">
-        <v>1020036</v>
+        <v>1020044</v>
       </c>
       <c r="B300" s="5">
         <v>102</v>
       </c>
       <c r="C300" s="5">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D300" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E300" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F300" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G300" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H300" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I300" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" s="5">
-        <v>1020037</v>
+        <v>1020045</v>
       </c>
       <c r="B301" s="5">
         <v>102</v>
       </c>
       <c r="C301" s="5">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D301" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E301" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F301" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G301" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H301" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I301" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" s="5">
-        <v>1020038</v>
+        <v>1020046</v>
       </c>
       <c r="B302" s="5">
         <v>102</v>
       </c>
       <c r="C302" s="5">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D302" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E302" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F302" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G302" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H302" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I302" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" s="5">
-        <v>1020039</v>
+        <v>1020047</v>
       </c>
       <c r="B303" s="5">
         <v>102</v>
       </c>
       <c r="C303" s="5">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D303" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E303" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F303" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G303" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H303" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I303" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" s="5">
-        <v>1020040</v>
+        <v>1020048</v>
       </c>
       <c r="B304" s="5">
         <v>102</v>
       </c>
       <c r="C304" s="5">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D304" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E304" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F304" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G304" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H304" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I304" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" s="5">
-        <v>1020041</v>
+        <v>1020049</v>
       </c>
       <c r="B305" s="5">
         <v>102</v>
       </c>
       <c r="C305" s="5">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D305" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E305" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F305" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G305" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H305" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I305" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" s="5">
-        <v>1020042</v>
+        <v>1020050</v>
       </c>
       <c r="B306" s="5">
         <v>102</v>
       </c>
       <c r="C306" s="5">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D306" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E306" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F306" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G306" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H306" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I306" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" s="5">
-        <v>1020043</v>
+        <v>1020051</v>
       </c>
       <c r="B307" s="5">
         <v>102</v>
       </c>
       <c r="C307" s="5">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D307" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E307" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F307" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G307" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H307" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I307" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" s="5">
-        <v>1020044</v>
+        <v>1020052</v>
       </c>
       <c r="B308" s="5">
         <v>102</v>
       </c>
       <c r="C308" s="5">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D308" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E308" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F308" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G308" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H308" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I308" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" s="5">
-        <v>1020045</v>
+        <v>1020053</v>
       </c>
       <c r="B309" s="5">
         <v>102</v>
       </c>
       <c r="C309" s="5">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D309" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E309" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F309" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G309" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H309" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I309" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" s="5">
-        <v>1020046</v>
+        <v>1020054</v>
       </c>
       <c r="B310" s="5">
         <v>102</v>
       </c>
       <c r="C310" s="5">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D310" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E310" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F310" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G310" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H310" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I310" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" s="5">
-        <v>1020047</v>
+        <v>1020055</v>
       </c>
       <c r="B311" s="5">
         <v>102</v>
       </c>
       <c r="C311" s="5">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D311" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E311" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F311" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G311" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H311" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I311" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" s="5">
-        <v>1020048</v>
+        <v>1020056</v>
       </c>
       <c r="B312" s="5">
         <v>102</v>
       </c>
       <c r="C312" s="5">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D312" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E312" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F312" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G312" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H312" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I312" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" s="5">
-        <v>1020049</v>
+        <v>1020057</v>
       </c>
       <c r="B313" s="5">
         <v>102</v>
       </c>
       <c r="C313" s="5">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D313" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E313" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F313" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G313" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H313" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I313" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" s="5">
-        <v>1020050</v>
+        <v>1020058</v>
       </c>
       <c r="B314" s="5">
         <v>102</v>
       </c>
       <c r="C314" s="5">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D314" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E314" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F314" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G314" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H314" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I314" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" s="5">
-        <v>1020051</v>
+        <v>1020059</v>
       </c>
       <c r="B315" s="5">
         <v>102</v>
       </c>
       <c r="C315" s="5">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D315" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E315" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F315" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G315" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H315" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I315" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" s="5">
-        <v>1020052</v>
+        <v>1020060</v>
       </c>
       <c r="B316" s="5">
         <v>102</v>
       </c>
       <c r="C316" s="5">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D316" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E316" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F316" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G316" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H316" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I316" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" s="5">
-        <v>1020053</v>
+        <v>1030002</v>
       </c>
       <c r="B317" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C317" s="5">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D317" t="s">
         <v>34</v>
@@ -9731,19 +9727,19 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" s="5">
-        <v>1020054</v>
+        <v>1030003</v>
       </c>
       <c r="B318" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C318" s="5">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="D318" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E318" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F318" t="s">
         <v>34</v>
@@ -9760,19 +9756,19 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" s="5">
-        <v>1020055</v>
+        <v>1030004</v>
       </c>
       <c r="B319" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C319" s="5">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="D319" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E319" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F319" t="s">
         <v>34</v>
@@ -9789,22 +9785,22 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" s="5">
-        <v>1020056</v>
+        <v>1030005</v>
       </c>
       <c r="B320" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C320" s="5">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="D320" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E320" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F320" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G320" t="s">
         <v>34</v>
@@ -9818,22 +9814,22 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" s="5">
-        <v>1020057</v>
+        <v>1030006</v>
       </c>
       <c r="B321" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C321" s="5">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="D321" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E321" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F321" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G321" t="s">
         <v>34</v>
@@ -9847,22 +9843,22 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" s="5">
-        <v>1020058</v>
+        <v>1030007</v>
       </c>
       <c r="B322" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C322" s="5">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="D322" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E322" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F322" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G322" t="s">
         <v>34</v>
@@ -9876,22 +9872,22 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" s="5">
-        <v>1020059</v>
+        <v>1030008</v>
       </c>
       <c r="B323" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C323" s="5">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D323" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E323" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F323" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G323" t="s">
         <v>34</v>
@@ -9905,22 +9901,22 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" s="5">
-        <v>1020060</v>
+        <v>1030009</v>
       </c>
       <c r="B324" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C324" s="5">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="D324" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E324" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F324" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G324" t="s">
         <v>34</v>
@@ -9934,13 +9930,13 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A325" s="5">
-        <v>1030001</v>
+        <v>1030010</v>
       </c>
       <c r="B325" s="5">
         <v>103</v>
       </c>
       <c r="C325" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D325" t="s">
         <v>35</v>
@@ -9949,27 +9945,27 @@
         <v>35</v>
       </c>
       <c r="F325" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G325" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H325" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I325" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" s="5">
-        <v>1030002</v>
+        <v>1030011</v>
       </c>
       <c r="B326" s="5">
         <v>103</v>
       </c>
       <c r="C326" s="5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D326" t="s">
         <v>35</v>
@@ -9978,828 +9974,567 @@
         <v>35</v>
       </c>
       <c r="F326" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G326" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H326" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I326" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" s="5">
-        <v>1030003</v>
+        <v>1030012</v>
       </c>
       <c r="B327" s="5">
         <v>103</v>
       </c>
       <c r="C327" s="5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D327" t="s">
+        <v>35</v>
+      </c>
+      <c r="E327" t="s">
+        <v>35</v>
+      </c>
+      <c r="F327" t="s">
         <v>36</v>
       </c>
-      <c r="E327" t="s">
-        <v>36</v>
-      </c>
-      <c r="F327" t="s">
-        <v>35</v>
-      </c>
       <c r="G327" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H327" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I327" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" s="5">
-        <v>1030004</v>
+        <v>1030013</v>
       </c>
       <c r="B328" s="5">
         <v>103</v>
       </c>
       <c r="C328" s="5">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D328" t="s">
+        <v>35</v>
+      </c>
+      <c r="E328" t="s">
+        <v>35</v>
+      </c>
+      <c r="F328" t="s">
         <v>36</v>
       </c>
-      <c r="E328" t="s">
-        <v>36</v>
-      </c>
-      <c r="F328" t="s">
-        <v>37</v>
-      </c>
       <c r="G328" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H328" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I328" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" s="5">
-        <v>1030005</v>
+        <v>1030014</v>
       </c>
       <c r="B329" s="5">
         <v>103</v>
       </c>
       <c r="C329" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D329" t="s">
+        <v>35</v>
+      </c>
+      <c r="E329" t="s">
+        <v>35</v>
+      </c>
+      <c r="F329" t="s">
         <v>36</v>
       </c>
-      <c r="E329" t="s">
-        <v>36</v>
-      </c>
-      <c r="F329" t="s">
-        <v>37</v>
-      </c>
       <c r="G329" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H329" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I329" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" s="5">
-        <v>1030006</v>
+        <v>1030015</v>
       </c>
       <c r="B330" s="5">
         <v>103</v>
       </c>
       <c r="C330" s="5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D330" t="s">
+        <v>35</v>
+      </c>
+      <c r="E330" t="s">
+        <v>35</v>
+      </c>
+      <c r="F330" t="s">
         <v>36</v>
       </c>
-      <c r="E330" t="s">
-        <v>36</v>
-      </c>
-      <c r="F330" t="s">
-        <v>37</v>
-      </c>
       <c r="G330" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H330" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I330" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" s="5">
-        <v>1030007</v>
+        <v>1030016</v>
       </c>
       <c r="B331" s="5">
         <v>103</v>
       </c>
       <c r="C331" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D331" t="s">
+        <v>35</v>
+      </c>
+      <c r="E331" t="s">
+        <v>35</v>
+      </c>
+      <c r="F331" t="s">
         <v>36</v>
       </c>
-      <c r="E331" t="s">
-        <v>36</v>
-      </c>
-      <c r="F331" t="s">
-        <v>37</v>
-      </c>
       <c r="G331" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H331" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I331" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" s="5">
-        <v>1030008</v>
+        <v>1030017</v>
       </c>
       <c r="B332" s="5">
         <v>103</v>
       </c>
       <c r="C332" s="5">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D332" t="s">
+        <v>35</v>
+      </c>
+      <c r="E332" t="s">
+        <v>35</v>
+      </c>
+      <c r="F332" t="s">
         <v>36</v>
       </c>
-      <c r="E332" t="s">
-        <v>36</v>
-      </c>
-      <c r="F332" t="s">
-        <v>37</v>
-      </c>
       <c r="G332" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H332" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I332" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" s="5">
-        <v>1030009</v>
+        <v>1030018</v>
       </c>
       <c r="B333" s="5">
         <v>103</v>
       </c>
       <c r="C333" s="5">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D333" t="s">
+        <v>35</v>
+      </c>
+      <c r="E333" t="s">
+        <v>35</v>
+      </c>
+      <c r="F333" t="s">
         <v>36</v>
       </c>
-      <c r="E333" t="s">
-        <v>36</v>
-      </c>
-      <c r="F333" t="s">
-        <v>37</v>
-      </c>
       <c r="G333" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H333" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I333" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" s="5">
-        <v>1030010</v>
+        <v>1030019</v>
       </c>
       <c r="B334" s="5">
         <v>103</v>
       </c>
       <c r="C334" s="5">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D334" t="s">
+        <v>35</v>
+      </c>
+      <c r="E334" t="s">
+        <v>35</v>
+      </c>
+      <c r="F334" t="s">
         <v>36</v>
       </c>
-      <c r="E334" t="s">
-        <v>36</v>
-      </c>
-      <c r="F334" t="s">
-        <v>37</v>
-      </c>
       <c r="G334" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H334" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I334" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" s="5">
-        <v>1030011</v>
+        <v>1030020</v>
       </c>
       <c r="B335" s="5">
         <v>103</v>
       </c>
       <c r="C335" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D335" t="s">
+        <v>35</v>
+      </c>
+      <c r="E335" t="s">
+        <v>35</v>
+      </c>
+      <c r="F335" t="s">
         <v>36</v>
       </c>
-      <c r="E335" t="s">
-        <v>36</v>
-      </c>
-      <c r="F335" t="s">
-        <v>37</v>
-      </c>
       <c r="G335" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H335" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I335" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" s="5">
-        <v>1030012</v>
+        <v>1030021</v>
       </c>
       <c r="B336" s="5">
         <v>103</v>
       </c>
       <c r="C336" s="5">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D336" t="s">
+        <v>35</v>
+      </c>
+      <c r="E336" t="s">
+        <v>35</v>
+      </c>
+      <c r="F336" t="s">
         <v>36</v>
       </c>
-      <c r="E336" t="s">
-        <v>36</v>
-      </c>
-      <c r="F336" t="s">
-        <v>37</v>
-      </c>
       <c r="G336" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H336" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I336" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" s="5">
-        <v>1030013</v>
+        <v>1030022</v>
       </c>
       <c r="B337" s="5">
         <v>103</v>
       </c>
       <c r="C337" s="5">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D337" t="s">
+        <v>35</v>
+      </c>
+      <c r="E337" t="s">
+        <v>35</v>
+      </c>
+      <c r="F337" t="s">
         <v>36</v>
       </c>
-      <c r="E337" t="s">
-        <v>36</v>
-      </c>
-      <c r="F337" t="s">
-        <v>37</v>
-      </c>
       <c r="G337" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H337" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I337" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338" s="5">
-        <v>1030014</v>
+        <v>1030023</v>
       </c>
       <c r="B338" s="5">
         <v>103</v>
       </c>
       <c r="C338" s="5">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D338" t="s">
+        <v>35</v>
+      </c>
+      <c r="E338" t="s">
+        <v>35</v>
+      </c>
+      <c r="F338" t="s">
         <v>36</v>
       </c>
-      <c r="E338" t="s">
-        <v>36</v>
-      </c>
-      <c r="F338" t="s">
-        <v>37</v>
-      </c>
       <c r="G338" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H338" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I338" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339" s="5">
-        <v>1030015</v>
+        <v>1030024</v>
       </c>
       <c r="B339" s="5">
         <v>103</v>
       </c>
       <c r="C339" s="5">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D339" t="s">
+        <v>35</v>
+      </c>
+      <c r="E339" t="s">
+        <v>35</v>
+      </c>
+      <c r="F339" t="s">
         <v>36</v>
       </c>
-      <c r="E339" t="s">
-        <v>36</v>
-      </c>
-      <c r="F339" t="s">
-        <v>37</v>
-      </c>
       <c r="G339" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H339" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I339" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340" s="5">
-        <v>1030016</v>
+        <v>1030025</v>
       </c>
       <c r="B340" s="5">
         <v>103</v>
       </c>
       <c r="C340" s="5">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D340" t="s">
+        <v>35</v>
+      </c>
+      <c r="E340" t="s">
+        <v>35</v>
+      </c>
+      <c r="F340" t="s">
         <v>36</v>
       </c>
-      <c r="E340" t="s">
-        <v>36</v>
-      </c>
-      <c r="F340" t="s">
-        <v>37</v>
-      </c>
       <c r="G340" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H340" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I340" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" s="5">
-        <v>1030017</v>
+        <v>1030026</v>
       </c>
       <c r="B341" s="5">
         <v>103</v>
       </c>
       <c r="C341" s="5">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D341" t="s">
+        <v>35</v>
+      </c>
+      <c r="E341" t="s">
+        <v>35</v>
+      </c>
+      <c r="F341" t="s">
         <v>36</v>
       </c>
-      <c r="E341" t="s">
-        <v>36</v>
-      </c>
-      <c r="F341" t="s">
-        <v>37</v>
-      </c>
       <c r="G341" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H341" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I341" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342" s="5">
-        <v>1030018</v>
+        <v>1030027</v>
       </c>
       <c r="B342" s="5">
         <v>103</v>
       </c>
       <c r="C342" s="5">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D342" t="s">
+        <v>35</v>
+      </c>
+      <c r="E342" t="s">
+        <v>35</v>
+      </c>
+      <c r="F342" t="s">
         <v>36</v>
       </c>
-      <c r="E342" t="s">
-        <v>36</v>
-      </c>
-      <c r="F342" t="s">
-        <v>37</v>
-      </c>
       <c r="G342" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H342" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I342" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343" s="5">
-        <v>1030019</v>
+        <v>1030028</v>
       </c>
       <c r="B343" s="5">
         <v>103</v>
       </c>
       <c r="C343" s="5">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D343" t="s">
+        <v>35</v>
+      </c>
+      <c r="E343" t="s">
+        <v>35</v>
+      </c>
+      <c r="F343" t="s">
         <v>36</v>
       </c>
-      <c r="E343" t="s">
-        <v>36</v>
-      </c>
-      <c r="F343" t="s">
-        <v>37</v>
-      </c>
       <c r="G343" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H343" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I343" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" s="5">
-        <v>1030020</v>
+        <v>1030029</v>
       </c>
       <c r="B344" s="5">
         <v>103</v>
       </c>
       <c r="C344" s="5">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D344" t="s">
+        <v>35</v>
+      </c>
+      <c r="E344" t="s">
+        <v>35</v>
+      </c>
+      <c r="F344" t="s">
         <v>36</v>
       </c>
-      <c r="E344" t="s">
-        <v>36</v>
-      </c>
-      <c r="F344" t="s">
-        <v>37</v>
-      </c>
       <c r="G344" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H344" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I344" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" s="5">
-        <v>1030021</v>
+        <v>1030030</v>
       </c>
       <c r="B345" s="5">
         <v>103</v>
       </c>
       <c r="C345" s="5">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D345" t="s">
+        <v>35</v>
+      </c>
+      <c r="E345" t="s">
+        <v>35</v>
+      </c>
+      <c r="F345" t="s">
         <v>36</v>
       </c>
-      <c r="E345" t="s">
-        <v>36</v>
-      </c>
-      <c r="F345" t="s">
-        <v>37</v>
-      </c>
       <c r="G345" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H345" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I345" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A346" s="5">
-        <v>1030022</v>
-      </c>
-      <c r="B346" s="5">
-        <v>103</v>
-      </c>
-      <c r="C346" s="5">
-        <v>22</v>
-      </c>
-      <c r="D346" t="s">
-        <v>36</v>
-      </c>
-      <c r="E346" t="s">
-        <v>36</v>
-      </c>
-      <c r="F346" t="s">
-        <v>37</v>
-      </c>
-      <c r="G346" t="s">
-        <v>35</v>
-      </c>
-      <c r="H346" t="s">
-        <v>35</v>
-      </c>
-      <c r="I346" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A347" s="5">
-        <v>1030023</v>
-      </c>
-      <c r="B347" s="5">
-        <v>103</v>
-      </c>
-      <c r="C347" s="5">
-        <v>23</v>
-      </c>
-      <c r="D347" t="s">
-        <v>36</v>
-      </c>
-      <c r="E347" t="s">
-        <v>36</v>
-      </c>
-      <c r="F347" t="s">
-        <v>37</v>
-      </c>
-      <c r="G347" t="s">
-        <v>35</v>
-      </c>
-      <c r="H347" t="s">
-        <v>35</v>
-      </c>
-      <c r="I347" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A348" s="5">
-        <v>1030024</v>
-      </c>
-      <c r="B348" s="5">
-        <v>103</v>
-      </c>
-      <c r="C348" s="5">
-        <v>24</v>
-      </c>
-      <c r="D348" t="s">
-        <v>36</v>
-      </c>
-      <c r="E348" t="s">
-        <v>36</v>
-      </c>
-      <c r="F348" t="s">
-        <v>37</v>
-      </c>
-      <c r="G348" t="s">
-        <v>35</v>
-      </c>
-      <c r="H348" t="s">
-        <v>35</v>
-      </c>
-      <c r="I348" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A349" s="5">
-        <v>1030025</v>
-      </c>
-      <c r="B349" s="5">
-        <v>103</v>
-      </c>
-      <c r="C349" s="5">
-        <v>25</v>
-      </c>
-      <c r="D349" t="s">
-        <v>36</v>
-      </c>
-      <c r="E349" t="s">
-        <v>36</v>
-      </c>
-      <c r="F349" t="s">
-        <v>37</v>
-      </c>
-      <c r="G349" t="s">
-        <v>35</v>
-      </c>
-      <c r="H349" t="s">
-        <v>35</v>
-      </c>
-      <c r="I349" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A350" s="5">
-        <v>1030026</v>
-      </c>
-      <c r="B350" s="5">
-        <v>103</v>
-      </c>
-      <c r="C350" s="5">
-        <v>26</v>
-      </c>
-      <c r="D350" t="s">
-        <v>36</v>
-      </c>
-      <c r="E350" t="s">
-        <v>36</v>
-      </c>
-      <c r="F350" t="s">
-        <v>37</v>
-      </c>
-      <c r="G350" t="s">
-        <v>35</v>
-      </c>
-      <c r="H350" t="s">
-        <v>35</v>
-      </c>
-      <c r="I350" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A351" s="5">
-        <v>1030027</v>
-      </c>
-      <c r="B351" s="5">
-        <v>103</v>
-      </c>
-      <c r="C351" s="5">
-        <v>27</v>
-      </c>
-      <c r="D351" t="s">
-        <v>36</v>
-      </c>
-      <c r="E351" t="s">
-        <v>36</v>
-      </c>
-      <c r="F351" t="s">
-        <v>37</v>
-      </c>
-      <c r="G351" t="s">
-        <v>35</v>
-      </c>
-      <c r="H351" t="s">
-        <v>35</v>
-      </c>
-      <c r="I351" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A352" s="5">
-        <v>1030028</v>
-      </c>
-      <c r="B352" s="5">
-        <v>103</v>
-      </c>
-      <c r="C352" s="5">
-        <v>28</v>
-      </c>
-      <c r="D352" t="s">
-        <v>36</v>
-      </c>
-      <c r="E352" t="s">
-        <v>36</v>
-      </c>
-      <c r="F352" t="s">
-        <v>37</v>
-      </c>
-      <c r="G352" t="s">
-        <v>35</v>
-      </c>
-      <c r="H352" t="s">
-        <v>35</v>
-      </c>
-      <c r="I352" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A353" s="5">
-        <v>1030029</v>
-      </c>
-      <c r="B353" s="5">
-        <v>103</v>
-      </c>
-      <c r="C353" s="5">
-        <v>29</v>
-      </c>
-      <c r="D353" t="s">
-        <v>36</v>
-      </c>
-      <c r="E353" t="s">
-        <v>36</v>
-      </c>
-      <c r="F353" t="s">
-        <v>37</v>
-      </c>
-      <c r="G353" t="s">
-        <v>35</v>
-      </c>
-      <c r="H353" t="s">
-        <v>35</v>
-      </c>
-      <c r="I353" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A354" s="5">
-        <v>1030030</v>
-      </c>
-      <c r="B354" s="5">
-        <v>103</v>
-      </c>
-      <c r="C354" s="5">
-        <v>30</v>
-      </c>
-      <c r="D354" t="s">
-        <v>36</v>
-      </c>
-      <c r="E354" t="s">
-        <v>36</v>
-      </c>
-      <c r="F354" t="s">
-        <v>37</v>
-      </c>
-      <c r="G354" t="s">
-        <v>35</v>
-      </c>
-      <c r="H354" t="s">
-        <v>35</v>
-      </c>
-      <c r="I354" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10FB981-F7C4-40BC-BEAC-BA6EBC818C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C9D3F9-FB44-4FF1-9B4B-4317AD8E0018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_rand_rule_v8" sheetId="1" r:id="rId1"/>
@@ -169,7 +169,7 @@
     <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100</t>
   </si>
   <si>
-    <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100_409:400</t>
+    <t>401:100_402:100_403:100_404:100_405:100_406:100_407:100_408:100_409:125</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -552,8 +552,9 @@
     <col min="1" max="1" width="17.625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.75" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="35.625" customWidth="1"/>
+    <col min="4" max="5" width="63" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="35.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
